--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F67CAB-5997-495D-8FEC-C9B673BAE022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACE534C-8BF0-4E96-9919-7D2BAA828587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -1883,264 +1883,6 @@
     <t>6603d7c7-806b-4518-84d5-6aff7b4afc6c</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC107_14_PC0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_4_MA0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_18_DISPEN.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_38_RA0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_39_HSYNC.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_40_VSYNC.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_1_A11.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_2_A12.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_3_A13.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_4_A14.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_5_A15.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_6_CLK.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_7_D4.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_8_D3.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_9_D5.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_10_D6.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_12_D2.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_13_D7.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_14_D0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_15_D1.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_16_INT.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_17_NMI.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_18_HALT.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_19_MREQ.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_20_IORQ.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_21_RD.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_22_WR.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_23_BUSAK.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_24_WAIT.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_25_BUSRQ.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_26_RESET.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_27_M1.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_28_RFSH.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_30_A0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_31_A1.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_32_A2.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_33_A3.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_34_A4.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_35_A5.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_36_A6.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_37_A7.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_38_A8.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_39_A9.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_40_A10.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_4_CCLK.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_5_NSYNC.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_8_B.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_10_G.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_12_R.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_14_NCPU.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_16_NCAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_19_NPHI.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_23_N244EN.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_24_CK16.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_31_NCASAD.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_33_NMWE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_34_NRAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope baseline/X101_1_CLK.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth tables/IC104_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth tables/IC105_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth tables/IC109_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth tables/IC113_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
     <t>Documentation of columns in this worksheet is availble here:</t>
   </si>
   <si>
@@ -2163,6 +1905,264 @@
   </si>
   <si>
     <t>Thumbnail highlight color</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC107_14_PC0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_4_MA0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_18_DISPEN.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_38_RA0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_39_HSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_40_VSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_1_A11.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_2_A12.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_3_A13.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_4_A14.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_5_A15.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_6_CLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_7_D4.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_8_D3.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_9_D5.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_10_D6.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_12_D2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_13_D7.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_14_D0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_15_D1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_16_INT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_17_NMI.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_18_HALT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_19_MREQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_20_IORQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_21_RD.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_22_WR.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_23_BUSAK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_24_WAIT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_25_BUSRQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_26_RESET.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_27_M1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_28_RFSH.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_30_A0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_31_A1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_32_A2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_33_A3.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_34_A4.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_35_A5.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_36_A6.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_37_A7.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_38_A8.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_39_A9.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_40_A10.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_4_CCLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_5_NSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_8_B.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_10_G.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_12_R.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_14_NCPU.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_16_NCAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_19_NPHI.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_23_N244EN.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_24_CK16.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_31_NCASAD.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_33_NMWE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_34_NRAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/X101_1_CLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC104_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC105_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC109_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC113_TRUTH_TABLE.jpg</t>
   </si>
   <si>
     <r>
@@ -2177,7 +2177,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-May-5</t>
+      <t>2026-May-7</t>
     </r>
   </si>
 </sst>
@@ -2503,11 +2503,11 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2529,9 +2529,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2569,7 +2569,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2675,7 +2675,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2817,7 +2817,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2827,16 +2827,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB56770-8233-4B8D-A81F-EDDC9713B054}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="76.21875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="38.7109375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="76.28515625" style="33" customWidth="1"/>
     <col min="3" max="5" width="14" style="33" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" style="33" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" style="33" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" style="33" customWidth="1"/>
-    <col min="9" max="9" width="38.5546875" style="33" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="33"/>
+    <col min="6" max="6" width="16.42578125" style="33" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" style="33" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="33" customWidth="1"/>
+    <col min="9" max="9" width="38.5703125" style="33" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="9" customFormat="1" ht="21">
@@ -2897,36 +2897,36 @@
         <v>34</v>
       </c>
       <c r="B8" s="14"/>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
       <c r="H8" s="54"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9" s="4" customFormat="1" ht="43.2">
+    <row r="9" spans="1:9" s="4" customFormat="1" ht="45">
       <c r="A9" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="62" t="s">
-        <v>667</v>
-      </c>
-      <c r="D9" s="62" t="s">
-        <v>668</v>
-      </c>
-      <c r="E9" s="62" t="s">
-        <v>669</v>
-      </c>
-      <c r="F9" s="62" t="s">
-        <v>670</v>
-      </c>
-      <c r="G9" s="62" t="s">
+      <c r="C9" s="61" t="s">
+        <v>581</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>583</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>584</v>
+      </c>
+      <c r="G9" s="61" t="s">
         <v>35</v>
       </c>
       <c r="H9" s="55" t="s">
@@ -3104,12 +3104,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCEBA5B-6A50-48EF-B74E-B76FA9984AEF}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
-    <col min="4" max="4" width="47.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+    <col min="4" max="4" width="47.7109375" customWidth="1"/>
     <col min="5" max="5" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3244,16 +3244,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1251FF9-425C-410E-B269-C7726F9C2504}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" style="1" customWidth="1"/>
     <col min="5" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="42.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.33203125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="42.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.28515625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">
@@ -3295,7 +3295,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="28.8">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="30">
       <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
@@ -4738,19 +4738,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D2A4B1-8E0B-46C6-8B83-02048610537D}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:L2883"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="95.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="73.6640625" style="44" customWidth="1"/>
-    <col min="11" max="11" width="49.88671875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="7.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.7109375" style="28" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="95.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="73.7109375" style="44" customWidth="1"/>
+    <col min="11" max="11" width="49.85546875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21">
@@ -4817,7 +4817,7 @@
       <c r="J7" s="46"/>
       <c r="K7" s="46"/>
     </row>
-    <row r="8" spans="1:12" s="6" customFormat="1" ht="28.8">
+    <row r="8" spans="1:12" s="6" customFormat="1" ht="30">
       <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="28.8">
+    <row r="10" spans="1:12" ht="30">
       <c r="A10" s="1" t="s">
         <v>130</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="115.2">
+    <row r="11" spans="1:12" ht="135">
       <c r="A11" s="9" t="s">
         <v>75</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.8">
+    <row r="12" spans="1:12" ht="30">
       <c r="A12" s="50" t="s">
         <v>75</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.8">
+    <row r="14" spans="1:12" ht="30">
       <c r="A14" s="1" t="s">
         <v>109</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="28.8">
+    <row r="15" spans="1:12" ht="30">
       <c r="A15" s="1" t="s">
         <v>109</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>171</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="J15" s="44" t="s">
         <v>172</v>
@@ -4983,7 +4983,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="28.8">
+    <row r="16" spans="1:12" ht="30">
       <c r="A16" s="1" t="s">
         <v>110</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="28.8">
+    <row r="17" spans="1:11" ht="30">
       <c r="A17" s="1" t="s">
         <v>110</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>171</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="J17" s="44" t="s">
         <v>172</v>
@@ -5031,7 +5031,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="57.6">
+    <row r="19" spans="1:11" ht="75">
       <c r="A19" s="9" t="s">
         <v>70</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="28.8">
+    <row r="20" spans="1:11" ht="30">
       <c r="A20" s="9" t="s">
         <v>70</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>253</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="J20" s="44" t="s">
         <v>225</v>
@@ -5099,7 +5099,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="43.2">
+    <row r="22" spans="1:11" ht="45">
       <c r="A22" s="9" t="s">
         <v>79</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>253</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="J22" s="44" t="s">
         <v>296</v>
@@ -5132,7 +5132,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="43.2">
+    <row r="23" spans="1:11" ht="45">
       <c r="A23" s="9" t="s">
         <v>79</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>253</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="J23" s="44" t="s">
         <v>294</v>
@@ -5165,7 +5165,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="43.2">
+    <row r="24" spans="1:11" ht="45">
       <c r="A24" s="9" t="s">
         <v>79</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>253</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="J24" s="44" t="s">
         <v>297</v>
@@ -5198,7 +5198,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="43.2">
+    <row r="25" spans="1:11" ht="45">
       <c r="A25" s="9" t="s">
         <v>79</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>253</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="J25" s="44" t="s">
         <v>295</v>
@@ -5231,7 +5231,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="43.2">
+    <row r="26" spans="1:11" ht="45">
       <c r="A26" s="9" t="s">
         <v>79</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>253</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="J26" s="44" t="s">
         <v>291</v>
@@ -5264,7 +5264,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="57.6">
+    <row r="27" spans="1:11" ht="60">
       <c r="A27" s="1" t="s">
         <v>111</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="28.8">
+    <row r="28" spans="1:11" ht="30">
       <c r="A28" s="1" t="s">
         <v>111</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>171</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="J28" s="44" t="s">
         <v>172</v>
@@ -5353,7 +5353,7 @@
         <v>253</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>515</v>
@@ -5386,7 +5386,7 @@
         <v>253</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>515</v>
@@ -5419,7 +5419,7 @@
         <v>253</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>515</v>
@@ -5452,7 +5452,7 @@
         <v>253</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>515</v>
@@ -5485,7 +5485,7 @@
         <v>253</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>515</v>
@@ -5494,7 +5494,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="43.2">
+    <row r="36" spans="1:11" ht="45">
       <c r="A36" s="59" t="s">
         <v>49</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>253</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>514</v>
@@ -5551,7 +5551,7 @@
         <v>253</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>515</v>
@@ -5584,7 +5584,7 @@
         <v>253</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>515</v>
@@ -5617,7 +5617,7 @@
         <v>253</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>515</v>
@@ -5650,7 +5650,7 @@
         <v>253</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>515</v>
@@ -5683,7 +5683,7 @@
         <v>253</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>515</v>
@@ -5716,7 +5716,7 @@
         <v>253</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>515</v>
@@ -5749,7 +5749,7 @@
         <v>253</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>515</v>
@@ -5782,7 +5782,7 @@
         <v>253</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>515</v>
@@ -5815,7 +5815,7 @@
         <v>253</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>554</v>
@@ -5848,7 +5848,7 @@
         <v>253</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>553</v>
@@ -5857,7 +5857,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="43.2">
+    <row r="47" spans="1:11" ht="45">
       <c r="A47" s="59" t="s">
         <v>49</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>253</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>520</v>
@@ -5890,7 +5890,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="43.2">
+    <row r="48" spans="1:11" ht="45">
       <c r="A48" s="59" t="s">
         <v>49</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>253</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>519</v>
@@ -5923,7 +5923,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="57.6">
+    <row r="49" spans="1:11" ht="60">
       <c r="A49" s="59" t="s">
         <v>49</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>253</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>518</v>
@@ -5980,7 +5980,7 @@
         <v>253</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>564</v>
@@ -6013,7 +6013,7 @@
         <v>253</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>565</v>
@@ -6046,7 +6046,7 @@
         <v>253</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>568</v>
@@ -6079,7 +6079,7 @@
         <v>253</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>558</v>
@@ -6112,7 +6112,7 @@
         <v>253</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>561</v>
@@ -6145,7 +6145,7 @@
         <v>253</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>562</v>
@@ -6154,7 +6154,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="43.2">
+    <row r="56" spans="1:11" ht="45">
       <c r="A56" s="59" t="s">
         <v>49</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>253</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>517</v>
@@ -6187,7 +6187,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="43.2">
+    <row r="57" spans="1:11" ht="45">
       <c r="A57" s="59" t="s">
         <v>49</v>
       </c>
@@ -6211,7 +6211,7 @@
         <v>253</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>516</v>
@@ -6244,7 +6244,7 @@
         <v>253</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>515</v>
@@ -6277,7 +6277,7 @@
         <v>253</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>515</v>
@@ -6310,7 +6310,7 @@
         <v>253</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>515</v>
@@ -6343,7 +6343,7 @@
         <v>253</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>515</v>
@@ -6376,7 +6376,7 @@
         <v>253</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>515</v>
@@ -6409,7 +6409,7 @@
         <v>253</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>515</v>
@@ -6442,7 +6442,7 @@
         <v>253</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>515</v>
@@ -6475,7 +6475,7 @@
         <v>253</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>515</v>
@@ -6508,7 +6508,7 @@
         <v>253</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>515</v>
@@ -6541,7 +6541,7 @@
         <v>253</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>515</v>
@@ -6574,7 +6574,7 @@
         <v>253</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>515</v>
@@ -6616,7 +6616,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="28.8">
+    <row r="71" spans="1:11" ht="30">
       <c r="A71" s="1" t="s">
         <v>112</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>171</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="J71" s="44" t="s">
         <v>172</v>
@@ -6661,7 +6661,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="144">
+    <row r="74" spans="1:11" ht="150">
       <c r="A74" s="9" t="s">
         <v>84</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="57.6">
+    <row r="75" spans="1:11" ht="60">
       <c r="A75" s="9" t="s">
         <v>84</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>253</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="J75" s="44" t="s">
         <v>254</v>
@@ -6713,7 +6713,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="43.2">
+    <row r="76" spans="1:11" ht="45">
       <c r="A76" s="9" t="s">
         <v>84</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>253</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="J76" s="44" t="s">
         <v>261</v>
@@ -6746,7 +6746,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="86.4">
+    <row r="77" spans="1:11" ht="90">
       <c r="A77" s="9" t="s">
         <v>84</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>253</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="J77" s="44" t="s">
         <v>258</v>
@@ -6779,7 +6779,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="86.4">
+    <row r="78" spans="1:11" ht="90">
       <c r="A78" s="9" t="s">
         <v>84</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>253</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="J78" s="44" t="s">
         <v>262</v>
@@ -6812,7 +6812,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="86.4">
+    <row r="79" spans="1:11" ht="90">
       <c r="A79" s="9" t="s">
         <v>84</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>253</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="J79" s="44" t="s">
         <v>263</v>
@@ -6845,7 +6845,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="57.6">
+    <row r="80" spans="1:11" ht="60">
       <c r="A80" s="9" t="s">
         <v>84</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>253</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="J80" s="44" t="s">
         <v>266</v>
@@ -6878,7 +6878,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="43.2">
+    <row r="81" spans="1:11" ht="45">
       <c r="A81" s="9" t="s">
         <v>84</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>253</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="J81" s="44" t="s">
         <v>277</v>
@@ -6911,7 +6911,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="43.2">
+    <row r="82" spans="1:11" ht="45">
       <c r="A82" s="9" t="s">
         <v>84</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>253</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="J82" s="44" t="s">
         <v>268</v>
@@ -6944,7 +6944,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="43.2">
+    <row r="83" spans="1:11" ht="45">
       <c r="A83" s="9" t="s">
         <v>84</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>253</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="J83" s="44" t="s">
         <v>272</v>
@@ -6977,7 +6977,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="43.2">
+    <row r="84" spans="1:11" ht="45">
       <c r="A84" s="9" t="s">
         <v>84</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>253</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="J84" s="44" t="s">
         <v>276</v>
@@ -7010,7 +7010,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="43.2">
+    <row r="85" spans="1:11" ht="45">
       <c r="A85" s="9" t="s">
         <v>84</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>253</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="J85" s="44" t="s">
         <v>281</v>
@@ -7043,7 +7043,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="43.2">
+    <row r="86" spans="1:11" ht="45">
       <c r="A86" s="9" t="s">
         <v>84</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>253</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="J86" s="44" t="s">
         <v>275</v>
@@ -7076,7 +7076,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="43.2">
+    <row r="87" spans="1:11" ht="45">
       <c r="A87" s="9" t="s">
         <v>84</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>253</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="J87" s="44" t="s">
         <v>280</v>
@@ -7109,7 +7109,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="57.6">
+    <row r="88" spans="1:11" ht="60">
       <c r="A88" s="50" t="s">
         <v>91</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>253</v>
       </c>
       <c r="I89" s="41" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="J89" s="52" t="s">
         <v>189</v>
@@ -7186,7 +7186,7 @@
         <v>253</v>
       </c>
       <c r="I90" s="41" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="J90" s="52" t="s">
         <v>187</v>
@@ -7219,7 +7219,7 @@
         <v>253</v>
       </c>
       <c r="I91" s="41" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="J91" s="52" t="s">
         <v>185</v>
@@ -7228,7 +7228,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="72">
+    <row r="92" spans="1:11" ht="75">
       <c r="A92" s="50" t="s">
         <v>91</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="57.6">
+    <row r="93" spans="1:11" ht="60">
       <c r="A93" s="50" t="s">
         <v>93</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>253</v>
       </c>
       <c r="I94" s="41" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="J94" s="52" t="s">
         <v>189</v>
@@ -7327,7 +7327,7 @@
         <v>253</v>
       </c>
       <c r="I95" s="41" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="J95" s="52" t="s">
         <v>187</v>
@@ -7360,7 +7360,7 @@
         <v>253</v>
       </c>
       <c r="I96" s="41" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="J96" s="52" t="s">
         <v>185</v>
@@ -7369,7 +7369,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="72">
+    <row r="97" spans="1:11" ht="75">
       <c r="A97" s="50" t="s">
         <v>93</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="57.6">
+    <row r="98" spans="1:11" ht="60">
       <c r="A98" s="50" t="s">
         <v>94</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>253</v>
       </c>
       <c r="I99" s="41" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="J99" s="52" t="s">
         <v>189</v>
@@ -7468,7 +7468,7 @@
         <v>253</v>
       </c>
       <c r="I100" s="41" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="J100" s="52" t="s">
         <v>187</v>
@@ -7501,7 +7501,7 @@
         <v>253</v>
       </c>
       <c r="I101" s="41" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="J101" s="52" t="s">
         <v>185</v>
@@ -7510,7 +7510,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="72">
+    <row r="102" spans="1:11" ht="75">
       <c r="A102" s="50" t="s">
         <v>94</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="57.6">
+    <row r="103" spans="1:11" ht="60">
       <c r="A103" s="50" t="s">
         <v>95</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>253</v>
       </c>
       <c r="I104" s="41" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="J104" s="52" t="s">
         <v>189</v>
@@ -7609,7 +7609,7 @@
         <v>253</v>
       </c>
       <c r="I105" s="41" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="J105" s="52" t="s">
         <v>187</v>
@@ -7642,7 +7642,7 @@
         <v>253</v>
       </c>
       <c r="I106" s="41" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="J106" s="52" t="s">
         <v>185</v>
@@ -7651,7 +7651,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="72">
+    <row r="107" spans="1:11" ht="75">
       <c r="A107" s="50" t="s">
         <v>95</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="57.6">
+    <row r="108" spans="1:11" ht="60">
       <c r="A108" s="50" t="s">
         <v>96</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>253</v>
       </c>
       <c r="I109" s="41" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="J109" s="52" t="s">
         <v>189</v>
@@ -7750,7 +7750,7 @@
         <v>253</v>
       </c>
       <c r="I110" s="41" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="J110" s="52" t="s">
         <v>187</v>
@@ -7783,7 +7783,7 @@
         <v>253</v>
       </c>
       <c r="I111" s="41" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="J111" s="52" t="s">
         <v>185</v>
@@ -7792,7 +7792,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="72">
+    <row r="112" spans="1:11" ht="75">
       <c r="A112" s="50" t="s">
         <v>96</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="57.6">
+    <row r="113" spans="1:11" ht="60">
       <c r="A113" s="50" t="s">
         <v>97</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>253</v>
       </c>
       <c r="I114" s="41" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="J114" s="52" t="s">
         <v>189</v>
@@ -7891,7 +7891,7 @@
         <v>253</v>
       </c>
       <c r="I115" s="41" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="J115" s="52" t="s">
         <v>187</v>
@@ -7924,7 +7924,7 @@
         <v>253</v>
       </c>
       <c r="I116" s="41" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="J116" s="52" t="s">
         <v>185</v>
@@ -7933,7 +7933,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="72">
+    <row r="117" spans="1:11" ht="75">
       <c r="A117" s="50" t="s">
         <v>97</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="57.6">
+    <row r="118" spans="1:11" ht="60">
       <c r="A118" s="50" t="s">
         <v>98</v>
       </c>
@@ -7999,7 +7999,7 @@
         <v>253</v>
       </c>
       <c r="I119" s="41" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="J119" s="52" t="s">
         <v>189</v>
@@ -8032,7 +8032,7 @@
         <v>253</v>
       </c>
       <c r="I120" s="41" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="J120" s="52" t="s">
         <v>187</v>
@@ -8065,7 +8065,7 @@
         <v>253</v>
       </c>
       <c r="I121" s="41" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="J121" s="52" t="s">
         <v>185</v>
@@ -8074,7 +8074,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="72">
+    <row r="122" spans="1:11" ht="75">
       <c r="A122" s="50" t="s">
         <v>98</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="57.6">
+    <row r="123" spans="1:11" ht="60">
       <c r="A123" s="50" t="s">
         <v>99</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>253</v>
       </c>
       <c r="I124" s="41" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="J124" s="52" t="s">
         <v>189</v>
@@ -8173,7 +8173,7 @@
         <v>253</v>
       </c>
       <c r="I125" s="41" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="J125" s="52" t="s">
         <v>187</v>
@@ -8206,7 +8206,7 @@
         <v>253</v>
       </c>
       <c r="I126" s="41" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="J126" s="52" t="s">
         <v>185</v>
@@ -8215,7 +8215,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="72">
+    <row r="127" spans="1:11" ht="75">
       <c r="A127" s="50" t="s">
         <v>99</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="57.6">
+    <row r="128" spans="1:11" ht="60">
       <c r="A128" s="1" t="s">
         <v>136</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>253</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="J130" s="44" t="s">
         <v>157</v>
@@ -11094,15 +11094,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD30A18-04B8-42E0-9E13-F4ED24029528}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:H587"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42.5546875" style="33" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="27" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="27" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="27" bestFit="1"/>
-    <col min="7" max="16384" width="8.88671875" style="33"/>
+    <col min="1" max="1" width="42.5703125" style="33" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="27" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="27" bestFit="1"/>
+    <col min="7" max="16384" width="8.85546875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="9" customFormat="1" ht="21">
@@ -13437,11 +13437,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F00A795-F924-4957-BF24-7CBCF1582012}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
-    <col min="2" max="2" width="36.6640625" customWidth="1"/>
-    <col min="3" max="3" width="82.44140625" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
+    <col min="3" max="3" width="82.42578125" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13891,11 +13891,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" customWidth="1"/>
-    <col min="3" max="3" width="102.109375" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" customWidth="1"/>
+    <col min="3" max="3" width="102.140625" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14453,11 +14453,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01DEE13-8567-47C0-98EF-B4590CF5D2FE}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="107.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" customWidth="1"/>
+    <col min="3" max="3" width="107.28515625" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14571,11 +14571,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787D0651-AC56-4C79-A3A0-381B16C48D1E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
-    <col min="2" max="2" width="44.44140625" customWidth="1"/>
-    <col min="3" max="3" width="86.5546875" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.42578125" customWidth="1"/>
+    <col min="3" max="3" width="86.5703125" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14702,10 +14702,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0514719B-6A3E-4079-99EF-DEF4C6E82768}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="27.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="6" customFormat="1" ht="21">
@@ -14722,7 +14722,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
-        <v>663</v>
+        <v>577</v>
       </c>
       <c r="B4" s="4"/>
     </row>
@@ -14734,16 +14734,16 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>664</v>
+        <v>578</v>
       </c>
       <c r="B7" s="5"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>665</v>
+        <v>579</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>666</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" spans="1:4">

--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACE534C-8BF0-4E96-9919-7D2BAA828587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFEAD5D-45B7-436E-895E-3B4E9DD099CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -1907,262 +1907,262 @@
     <t>Thumbnail highlight color</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC107_14_PC0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_4_MA0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_18_DISPEN.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_38_RA0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_39_HSYNC.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_40_VSYNC.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_1_A11.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_2_A12.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_3_A13.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_4_A14.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_5_A15.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_6_CLK.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_7_D4.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_8_D3.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_9_D5.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_10_D6.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_12_D2.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_13_D7.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_14_D0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_15_D1.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_16_INT.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_17_NMI.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_18_HALT.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_19_MREQ.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_20_IORQ.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_21_RD.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_22_WR.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_23_BUSAK.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_24_WAIT.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_25_BUSRQ.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_26_RESET.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_27_M1.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_28_RFSH.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_30_A0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_31_A1.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_32_A2.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_33_A3.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_34_A4.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_35_A5.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_36_A6.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_37_A7.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_38_A8.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_39_A9.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_40_A10.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_4_CCLK.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_5_NSYNC.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_8_B.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_10_G.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_12_R.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_14_NCPU.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_16_NCAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_19_NPHI.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_23_N244EN.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_24_CK16.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_31_NCASAD.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_33_NMWE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_34_NRAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/X101_1_CLK.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC104_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC105_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC109_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC113_TRUTH_TABLE.jpg</t>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC107_14_PC0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_4_MA0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_18_DISPEN.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_38_RA0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_39_HSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_40_VSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_1_A11.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_2_A12.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_3_A13.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_4_A14.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_5_A15.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_6_CLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_7_D4.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_8_D3.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_9_D5.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_10_D6.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_12_D2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_13_D7.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_14_D0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_15_D1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_16_INT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_17_NMI.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_18_HALT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_19_MREQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_20_IORQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_21_RD.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_22_WR.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_23_BUSAK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_24_WAIT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_25_BUSRQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_26_RESET.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_27_M1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_28_RFSH.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_30_A0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_31_A1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_32_A2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_33_A3.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_34_A4.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_35_A5.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_36_A6.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_37_A7.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_38_A8.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_39_A9.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_40_A10.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_4_CCLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_5_NSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_8_B.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_10_G.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_12_R.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_14_NCPU.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_16_NCAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_19_NPHI.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_23_N244EN.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_24_CK16.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_31_NCASAD.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_33_NMWE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_34_NRAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/X101_1_CLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth tables/IC104_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth tables/IC105_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth tables/IC109_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth tables/IC113_TRUTH_TABLE.jpg</t>
   </si>
   <si>
     <r>
@@ -2177,7 +2177,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-May-7</t>
+      <t>2026-May-8</t>
     </r>
   </si>
 </sst>

--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464117EA-FC6F-4B27-A3BE-588595C2B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3419073-521C-40FC-9A4B-ECA78BF1B521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Credits" sheetId="13" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Component images'!$A$8:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Component images'!$A$8:$J$137</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="687">
   <si>
     <t>Name</t>
   </si>
@@ -778,9 +778,6 @@
 Schematic Pin Names are shown in brackets.</t>
   </si>
   <si>
-    <t>Output bit 0 of keyboard row scan, occurring 50 times a second, to BCD Decoder A (Pin 15).</t>
-  </si>
-  <si>
     <t>Dynamic Random Access Memory organised as 65,536 one-bit words.
 The Gate Array (GA) provides Row Address Strobe (RAS), Column Address Strobe (CAS) and Write Enable (WE) signals.</t>
   </si>
@@ -2144,6 +2141,74 @@
   </si>
   <si>
     <t>Amstrad CPC 664/MC0005A/Truth tables/IC113_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>PB1</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC107_19_PB1.jpg</t>
+  </si>
+  <si>
+    <t>1e4655ae-0259-436f-b2fc-7331beca1dea</t>
+  </si>
+  <si>
+    <t>PC2</t>
+  </si>
+  <si>
+    <t>Keyboard row scan, occurring 50 times a second, Output to BCD Decoder A (Pin 15).</t>
+  </si>
+  <si>
+    <t>Keyboard row scan, occurring 50 times a second. Output to BCD Decoder C (Pin 13).</t>
+  </si>
+  <si>
+    <t>Input from LK1 
+LK1,LK2,LK3 connect to PPI Port B, Bit1-3. The links select the manufacturer name (which is displayed by the BIOS in the power-up message).  
+See CPC Wiki for more information.</t>
+  </si>
+  <si>
+    <t>19783e4c-893a-43c3-acac-d61955db389c</t>
+  </si>
+  <si>
+    <t>PC1</t>
+  </si>
+  <si>
+    <t>Keyboard row scan, occurring 50 times a second, Output to BCD Decoder B (Pin 14).</t>
+  </si>
+  <si>
+    <t>52f3577c-d78f-47a8-9224-f4599615ced2</t>
+  </si>
+  <si>
+    <t>PC3</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC107_15_PC1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC107_16_PC2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC107_17_PC3.jpg</t>
+  </si>
+  <si>
+    <t>Keyboard row scan, occurring 50 times a second. Output to BCD Decoder D (Pin 12).</t>
+  </si>
+  <si>
+    <t>a446fca6-6fdf-47fe-8378-9e65a7430662</t>
+  </si>
+  <si>
+    <t>PB0</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC107_18_PB0.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input VSYNC 50Hz from CRTC (Pin 40). </t>
+  </si>
+  <si>
+    <t>b4a59efc-eb5a-4271-9bac-0647594da3c9</t>
   </si>
   <si>
     <r>
@@ -2158,7 +2223,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-May-8</t>
+      <t>2026-May-10</t>
     </r>
   </si>
 </sst>
@@ -2820,7 +2885,7 @@
     </row>
     <row r="3" spans="1:9" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2884,25 +2949,25 @@
         <v>16</v>
       </c>
       <c r="C9" s="57" t="s">
+        <v>574</v>
+      </c>
+      <c r="D9" s="57" t="s">
         <v>575</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="E9" s="57" t="s">
         <v>576</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="F9" s="57" t="s">
         <v>577</v>
-      </c>
-      <c r="F9" s="57" t="s">
-        <v>578</v>
       </c>
       <c r="G9" s="57" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="51" t="s">
+        <v>292</v>
+      </c>
+      <c r="I9" s="52" t="s">
         <v>293</v>
-      </c>
-      <c r="I9" s="52" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2910,7 +2975,7 @@
         <v>129</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2926,7 +2991,7 @@
       </c>
       <c r="H10" s="53"/>
       <c r="I10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2934,7 +2999,7 @@
         <v>128</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>5</v>
@@ -2950,7 +3015,7 @@
       </c>
       <c r="H11" s="53"/>
       <c r="I11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2974,7 +3039,7 @@
       </c>
       <c r="H12" s="53"/>
       <c r="I12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2982,7 +3047,7 @@
         <v>63</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>5</v>
@@ -2998,7 +3063,7 @@
       </c>
       <c r="H13" s="53"/>
       <c r="I13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3148,7 +3213,7 @@
         <v>14</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3156,7 +3221,7 @@
         <v>124</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>125</v>
@@ -3168,10 +3233,10 @@
         <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3194,7 +3259,7 @@
         <v>72</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3202,7 +3267,7 @@
         <v>99</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C11" s="1">
         <v>40022</v>
@@ -3214,10 +3279,10 @@
         <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3240,7 +3305,7 @@
         <v>109</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3263,7 +3328,7 @@
         <v>109</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3286,7 +3351,7 @@
         <v>136</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3309,7 +3374,7 @@
         <v>67</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3332,7 +3397,7 @@
         <v>76</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3355,7 +3420,7 @@
         <v>109</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3363,7 +3428,7 @@
         <v>119</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>121</v>
@@ -3378,7 +3443,7 @@
         <v>120</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3401,7 +3466,7 @@
         <v>56</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3409,7 +3474,7 @@
         <v>82</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>83</v>
@@ -3421,7 +3486,7 @@
         <v>17</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3444,7 +3509,7 @@
         <v>109</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3464,7 +3529,7 @@
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3472,7 +3537,7 @@
         <v>95</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>96</v>
@@ -3484,7 +3549,7 @@
         <v>17</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3507,7 +3572,7 @@
         <v>80</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3515,7 +3580,7 @@
         <v>85</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C25" s="1">
         <v>4164</v>
@@ -3530,7 +3595,7 @@
         <v>167</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3538,7 +3603,7 @@
         <v>87</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C26" s="1">
         <v>4164</v>
@@ -3553,7 +3618,7 @@
         <v>168</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3561,7 +3626,7 @@
         <v>88</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C27" s="1">
         <v>4164</v>
@@ -3576,7 +3641,7 @@
         <v>169</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3584,7 +3649,7 @@
         <v>89</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C28" s="1">
         <v>4164</v>
@@ -3599,7 +3664,7 @@
         <v>170</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3607,7 +3672,7 @@
         <v>90</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C29" s="1">
         <v>4164</v>
@@ -3622,7 +3687,7 @@
         <v>171</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3630,7 +3695,7 @@
         <v>91</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C30" s="1">
         <v>4164</v>
@@ -3645,7 +3710,7 @@
         <v>172</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3653,7 +3718,7 @@
         <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C31" s="1">
         <v>4164</v>
@@ -3668,7 +3733,7 @@
         <v>173</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3676,7 +3741,7 @@
         <v>93</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C32" s="1">
         <v>4164</v>
@@ -3691,7 +3756,7 @@
         <v>174</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3699,7 +3764,7 @@
         <v>130</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>131</v>
@@ -3711,7 +3776,7 @@
         <v>17</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3731,7 +3796,7 @@
         <v>145</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4567,7 +4632,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D2A4B1-8E0B-46C6-8B83-02048610537D}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:L2883"/>
+  <dimension ref="A1:L2888"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
@@ -4664,13 +4729,13 @@
         <v>38</v>
       </c>
       <c r="F8" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>244</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>1</v>
@@ -4679,7 +4744,7 @@
         <v>39</v>
       </c>
       <c r="K8" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -4696,7 +4761,7 @@
         <v>217</v>
       </c>
       <c r="K9" s="54" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L9" s="9"/>
     </row>
@@ -4714,7 +4779,7 @@
         <v>204</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="135">
@@ -4730,10 +4795,10 @@
         <v>188</v>
       </c>
       <c r="J11" s="40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30">
@@ -4752,10 +4817,10 @@
         <v>199</v>
       </c>
       <c r="J12" s="48" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="37" customFormat="1">
@@ -4776,7 +4841,7 @@
       </c>
       <c r="J13" s="40"/>
       <c r="K13" s="37" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="30">
@@ -4790,10 +4855,10 @@
         <v>117</v>
       </c>
       <c r="J14" s="40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30">
@@ -4804,13 +4869,13 @@
         <v>165</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="J15" s="40" t="s">
         <v>166</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="30">
@@ -4824,10 +4889,10 @@
         <v>117</v>
       </c>
       <c r="J16" s="40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30">
@@ -4838,13 +4903,13 @@
         <v>165</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="J17" s="40" t="s">
         <v>166</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4858,7 +4923,7 @@
         <v>137</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="75">
@@ -4877,7 +4942,7 @@
         <v>201</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30">
@@ -4895,466 +4960,466 @@
         <v>216</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I20" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J20" s="40" t="s">
-        <v>219</v>
+        <v>669</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30">
       <c r="A21" s="9" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B21" s="9"/>
-      <c r="C21" s="27"/>
+      <c r="C21" s="27">
+        <v>15</v>
+      </c>
       <c r="D21" s="1" t="s">
-        <v>19</v>
+        <v>673</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>277</v>
+        <v>677</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>674</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="45">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30">
       <c r="A22" s="9" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="27">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>278</v>
+        <v>668</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I22" s="1" t="s">
-        <v>580</v>
+        <v>678</v>
       </c>
       <c r="J22" s="40" t="s">
-        <v>290</v>
+        <v>670</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="45">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30">
       <c r="A23" s="9" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="27">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>279</v>
+        <v>676</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I23" s="1" t="s">
-        <v>581</v>
+        <v>679</v>
       </c>
       <c r="J23" s="40" t="s">
-        <v>288</v>
+        <v>680</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="45">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="9" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="27">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>280</v>
+        <v>682</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I24" s="1" t="s">
-        <v>582</v>
+        <v>683</v>
       </c>
       <c r="J24" s="40" t="s">
-        <v>291</v>
+        <v>684</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="45">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="90">
       <c r="A25" s="9" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="27">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>281</v>
+        <v>664</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>250</v>
+        <v>665</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I25" s="1" t="s">
-        <v>583</v>
+        <v>666</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="45">
+        <v>671</v>
+      </c>
+      <c r="K25" s="54" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B26" s="9"/>
-      <c r="C26" s="27">
+      <c r="C26" s="27"/>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="45">
+      <c r="A27" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="27">
+        <v>4</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="J27" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="45">
+      <c r="A28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="27">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J28" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="45">
+      <c r="A29" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="27">
+        <v>38</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="J29" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="45">
+      <c r="A30" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="27">
+        <v>39</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="J30" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="45">
+      <c r="A31" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="27">
         <v>40</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D31" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G26" s="1" t="s">
+      <c r="F31" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J26" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="I31" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="J31" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="60">
+      <c r="A32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J32" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="60">
-      <c r="A27" s="1" t="s">
+    <row r="33" spans="1:11" ht="30">
+      <c r="A33" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D33" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="J33" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J27" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="30">
-      <c r="A28" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="J28" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="K28" s="1" t="s">
+      <c r="I34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K34" s="54" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K29" s="54" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="23">
-        <v>1</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K31" s="54" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="23">
-        <v>2</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K32" s="54" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="23">
-        <v>3</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K33" s="54" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="23">
-        <v>4</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K34" s="54" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="53.25" customHeight="1">
+    <row r="35" spans="1:11">
       <c r="A35" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B35" s="12"/>
-      <c r="C35" s="23">
-        <v>5</v>
-      </c>
+      <c r="C35" s="23"/>
       <c r="D35" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K35" s="54" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="45">
+        <v>116</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="23">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I36" s="9" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>508</v>
       </c>
       <c r="K36" s="54" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -5363,31 +5428,31 @@
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I37" s="9" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
+      </c>
+      <c r="K37" s="54" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -5396,31 +5461,31 @@
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="23">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>494</v>
+        <v>527</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I38" s="9" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>502</v>
+        <v>508</v>
+      </c>
+      <c r="K38" s="54" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -5429,97 +5494,97 @@
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="23">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G39" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I39" s="9" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>508</v>
+      </c>
+      <c r="K39" s="54" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="53.25" customHeight="1">
       <c r="A40" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G40" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I40" s="9" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>508</v>
+      </c>
+      <c r="K40" s="54" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="45">
       <c r="A41" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="G41" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I41" s="9" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>501</v>
+        <v>507</v>
+      </c>
+      <c r="K41" s="54" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5528,31 +5593,31 @@
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="23">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G42" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I42" s="9" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K42" s="54" t="s">
-        <v>506</v>
+        <v>508</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5561,31 +5626,31 @@
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="23">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G43" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I43" s="9" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -5594,31 +5659,31 @@
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="23">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G44" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I44" s="9" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5627,31 +5692,31 @@
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="23">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>551</v>
+        <v>496</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I45" s="9" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="K45" s="54" t="s">
-        <v>569</v>
+        <v>508</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -5660,130 +5725,130 @@
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="23">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>550</v>
+        <v>492</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>482</v>
+        <v>216</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G46" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I46" s="9" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K46" s="54" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="45">
+        <v>508</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="23">
-        <v>18</v>
-      </c>
-      <c r="D47" s="31" t="s">
-        <v>481</v>
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>497</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>482</v>
+        <v>216</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G47" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I47" s="9" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="45">
+        <v>508</v>
+      </c>
+      <c r="K47" s="54" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="23">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F48" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I48" s="9" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="60">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="23">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I49" s="9" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5792,31 +5857,31 @@
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="23">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G50" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I50" s="9" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="K50" s="54" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5825,130 +5890,130 @@
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="23">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>216</v>
+        <v>481</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G51" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I51" s="9" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="K51" s="54" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="45">
       <c r="A52" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="23">
-        <v>23</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>561</v>
+        <v>18</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>480</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="G52" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H52" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I52" s="9" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="K52" s="54" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>513</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="45">
       <c r="A53" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="23">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>549</v>
+        <v>478</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I53" s="9" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="K53" s="54" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>512</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="60">
       <c r="A54" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="23">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>554</v>
+        <v>479</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>482</v>
+        <v>216</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="G54" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I54" s="9" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="K54" s="54" t="s">
-        <v>567</v>
+        <v>511</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -5957,97 +6022,97 @@
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="23">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>482</v>
+        <v>216</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G55" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I55" s="9" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K55" s="54" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="45">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="23">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>483</v>
+        <v>559</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G56" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I56" s="9" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="45">
+        <v>558</v>
+      </c>
+      <c r="K56" s="54" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="23">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>484</v>
+        <v>560</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>216</v>
+        <v>481</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G57" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I57" s="9" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>489</v>
+        <v>561</v>
+      </c>
+      <c r="K57" s="54" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -6056,31 +6121,31 @@
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="23">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="G58" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I58" s="9" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>509</v>
+        <v>551</v>
       </c>
       <c r="K58" s="54" t="s">
-        <v>531</v>
+        <v>565</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -6089,31 +6154,31 @@
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="23">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>517</v>
+        <v>553</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>216</v>
+        <v>481</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G59" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I59" s="9" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>509</v>
+        <v>554</v>
       </c>
       <c r="K59" s="54" t="s">
-        <v>532</v>
+        <v>566</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -6122,97 +6187,97 @@
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="23">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>518</v>
+        <v>552</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>216</v>
+        <v>481</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G60" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I60" s="9" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>509</v>
+        <v>555</v>
       </c>
       <c r="K60" s="54" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="45">
       <c r="A61" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="23">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G61" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I61" s="9" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K61" s="54" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>510</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="45">
       <c r="A62" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B62" s="12"/>
       <c r="C62" s="23">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>520</v>
+        <v>483</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G62" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I62" s="9" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="K62" s="54" t="s">
-        <v>535</v>
+      <c r="K62" s="1" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -6221,31 +6286,31 @@
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="23">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G63" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I63" s="9" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K63" s="54" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -6254,31 +6319,31 @@
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="23">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G64" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I64" s="9" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K64" s="54" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -6287,31 +6352,31 @@
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="23">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I65" s="9" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K65" s="54" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -6320,31 +6385,31 @@
       </c>
       <c r="B66" s="12"/>
       <c r="C66" s="23">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G66" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I66" s="9" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K66" s="54" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -6353,31 +6418,31 @@
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="23">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G67" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I67" s="9" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K67" s="54" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -6386,114 +6451,201 @@
       </c>
       <c r="B68" s="12"/>
       <c r="C68" s="23">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G68" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I68" s="9" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>541</v>
+        <v>508</v>
+      </c>
+      <c r="K68" s="54" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="12"/>
+      <c r="C69" s="23">
+        <v>36</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="K69" s="54" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="12"/>
+      <c r="C70" s="23">
+        <v>37</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="K70" s="54" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="12"/>
+      <c r="C71" s="23">
+        <v>38</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="K71" s="54" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" s="12"/>
+      <c r="C72" s="23">
+        <v>39</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="K72" s="54" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" s="12"/>
+      <c r="C73" s="23">
+        <v>40</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="67.5" customHeight="1">
-      <c r="A70" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J70" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="30">
-      <c r="A71" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="J71" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
-      <c r="A72" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="A73" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="150">
-      <c r="A74" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="27"/>
@@ -6501,178 +6653,91 @@
         <v>19</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J74" s="40" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="60">
-      <c r="A75" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B75" s="9"/>
-      <c r="C75" s="27">
-        <v>4</v>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="67.5" customHeight="1">
+      <c r="A75" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>623</v>
+        <v>117</v>
       </c>
       <c r="J75" s="40" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="45">
-      <c r="A76" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="27">
-        <v>5</v>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="30">
+      <c r="A76" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>247</v>
+        <v>165</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>624</v>
+        <v>663</v>
       </c>
       <c r="J76" s="40" t="s">
-        <v>255</v>
+        <v>166</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="90">
-      <c r="A77" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B77" s="9"/>
-      <c r="C77" s="27">
-        <v>8</v>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="J77" s="40" t="s">
-        <v>252</v>
+        <v>155</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="90">
-      <c r="A78" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="27">
-        <v>10</v>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="J78" s="40" t="s">
-        <v>256</v>
+        <v>157</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="90">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="150">
       <c r="A79" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B79" s="9"/>
-      <c r="C79" s="27">
-        <v>12</v>
-      </c>
+      <c r="C79" s="27"/>
       <c r="D79" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>627</v>
+        <v>164</v>
       </c>
       <c r="J79" s="40" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="60">
@@ -6681,31 +6746,31 @@
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="27">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>259</v>
+        <v>152</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F80" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G80" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="I80" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="J80" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="I80" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="J80" s="40" t="s">
-        <v>260</v>
-      </c>
       <c r="K80" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="45">
@@ -6714,163 +6779,163 @@
       </c>
       <c r="B81" s="9"/>
       <c r="C81" s="27">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="H81" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I81" s="1" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="J81" s="40" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="45">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="90">
       <c r="A82" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B82" s="9"/>
       <c r="C82" s="27">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="F82" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G82" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H82" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I82" s="1" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="J82" s="40" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="45">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="90">
       <c r="A83" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B83" s="9"/>
       <c r="C83" s="27">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G83" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H83" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I83" s="1" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="J83" s="40" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="45">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="90">
       <c r="A84" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B84" s="9"/>
       <c r="C84" s="27">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="G84" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H84" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I84" s="1" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="J84" s="40" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="45">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="60">
       <c r="A85" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B85" s="9"/>
       <c r="C85" s="27">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>216</v>
+        <v>153</v>
       </c>
       <c r="F85" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="H85" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I85" s="1" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="J85" s="40" t="s">
-        <v>275</v>
-      </c>
-      <c r="K85" s="54" t="s">
-        <v>432</v>
+        <v>259</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="45">
@@ -6879,31 +6944,31 @@
       </c>
       <c r="B86" s="9"/>
       <c r="C86" s="27">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>216</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="G86" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H86" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I86" s="1" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="J86" s="40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>433</v>
+        <v>477</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="45">
@@ -6912,177 +6977,201 @@
       </c>
       <c r="B87" s="9"/>
       <c r="C87" s="27">
+        <v>19</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J87" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="45">
+      <c r="A88" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B88" s="9"/>
+      <c r="C88" s="27">
+        <v>23</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J88" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="45">
+      <c r="A89" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B89" s="9"/>
+      <c r="C89" s="27">
+        <v>24</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="J89" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="45">
+      <c r="A90" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B90" s="9"/>
+      <c r="C90" s="27">
+        <v>31</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="J90" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="K90" s="54" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="45">
+      <c r="A91" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B91" s="9"/>
+      <c r="C91" s="27">
+        <v>33</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="J91" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="45">
+      <c r="A92" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B92" s="9"/>
+      <c r="C92" s="27">
         <v>34</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D92" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="G92" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="J92" s="40" t="s">
         <v>273</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="J87" s="40" t="s">
-        <v>274</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="60">
-      <c r="A88" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B88" s="46"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="37"/>
-      <c r="I88" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J88" s="48" t="s">
-        <v>220</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B89" s="46"/>
-      <c r="C89" s="47">
-        <v>3</v>
-      </c>
-      <c r="D89" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E89" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I89" s="37" t="s">
-        <v>636</v>
-      </c>
-      <c r="J89" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B90" s="46"/>
-      <c r="C90" s="47">
-        <v>4</v>
-      </c>
-      <c r="D90" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="E90" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I90" s="37" t="s">
-        <v>637</v>
-      </c>
-      <c r="J90" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B91" s="46"/>
-      <c r="C91" s="47">
-        <v>15</v>
-      </c>
-      <c r="D91" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="E91" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I91" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="J91" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="75">
-      <c r="A92" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B92" s="46"/>
-      <c r="C92" s="47"/>
-      <c r="D92" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="E92" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="I92" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="J92" s="48" t="s">
-        <v>197</v>
-      </c>
       <c r="K92" s="1" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="60">
       <c r="A93" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B93" s="46"/>
       <c r="C93" s="47"/>
@@ -7094,15 +7183,15 @@
         <v>156</v>
       </c>
       <c r="J93" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B94" s="46"/>
       <c r="C94" s="47">
@@ -7115,27 +7204,27 @@
         <v>216</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G94" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H94" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H94" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I94" s="37" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="J94" s="48" t="s">
         <v>183</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B95" s="46"/>
       <c r="C95" s="47">
@@ -7148,27 +7237,27 @@
         <v>216</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="H95" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I95" s="37" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="J95" s="48" t="s">
         <v>181</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B96" s="46"/>
       <c r="C96" s="47">
@@ -7181,27 +7270,27 @@
         <v>216</v>
       </c>
       <c r="F96" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G96" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="H96" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I96" s="37" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="J96" s="48" t="s">
         <v>179</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="75">
       <c r="A97" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B97" s="46"/>
       <c r="C97" s="47"/>
@@ -7218,12 +7307,12 @@
         <v>197</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="60">
       <c r="A98" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B98" s="46"/>
       <c r="C98" s="47"/>
@@ -7235,15 +7324,15 @@
         <v>156</v>
       </c>
       <c r="J98" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B99" s="46"/>
       <c r="C99" s="47">
@@ -7256,27 +7345,27 @@
         <v>216</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G99" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I99" s="37" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="J99" s="48" t="s">
         <v>183</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B100" s="46"/>
       <c r="C100" s="47">
@@ -7289,27 +7378,27 @@
         <v>216</v>
       </c>
       <c r="F100" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G100" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G100" s="1" t="s">
+      <c r="H100" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I100" s="37" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J100" s="48" t="s">
         <v>181</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B101" s="46"/>
       <c r="C101" s="47">
@@ -7322,27 +7411,27 @@
         <v>216</v>
       </c>
       <c r="F101" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G101" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="H101" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I101" s="37" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="J101" s="48" t="s">
         <v>179</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="75">
       <c r="A102" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B102" s="46"/>
       <c r="C102" s="47"/>
@@ -7359,12 +7448,12 @@
         <v>197</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="60">
       <c r="A103" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B103" s="46"/>
       <c r="C103" s="47"/>
@@ -7376,15 +7465,15 @@
         <v>156</v>
       </c>
       <c r="J103" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B104" s="46"/>
       <c r="C104" s="47">
@@ -7397,27 +7486,27 @@
         <v>216</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G104" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H104" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I104" s="37" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="J104" s="48" t="s">
         <v>183</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B105" s="46"/>
       <c r="C105" s="47">
@@ -7430,27 +7519,27 @@
         <v>216</v>
       </c>
       <c r="F105" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="H105" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I105" s="37" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="J105" s="48" t="s">
         <v>181</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B106" s="46"/>
       <c r="C106" s="47">
@@ -7463,27 +7552,27 @@
         <v>216</v>
       </c>
       <c r="F106" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G106" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="H106" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I106" s="37" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="J106" s="48" t="s">
         <v>179</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="75">
       <c r="A107" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B107" s="46"/>
       <c r="C107" s="47"/>
@@ -7500,12 +7589,12 @@
         <v>197</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="60">
       <c r="A108" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B108" s="46"/>
       <c r="C108" s="47"/>
@@ -7517,15 +7606,15 @@
         <v>156</v>
       </c>
       <c r="J108" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B109" s="46"/>
       <c r="C109" s="47">
@@ -7538,27 +7627,27 @@
         <v>216</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H109" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I109" s="37" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="J109" s="48" t="s">
         <v>183</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B110" s="46"/>
       <c r="C110" s="47">
@@ -7571,27 +7660,27 @@
         <v>216</v>
       </c>
       <c r="F110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G110" s="1" t="s">
+      <c r="H110" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H110" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I110" s="37" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="J110" s="48" t="s">
         <v>181</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B111" s="46"/>
       <c r="C111" s="47">
@@ -7604,27 +7693,27 @@
         <v>216</v>
       </c>
       <c r="F111" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G111" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G111" s="1" t="s">
+      <c r="H111" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I111" s="37" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J111" s="48" t="s">
         <v>179</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="75">
       <c r="A112" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B112" s="46"/>
       <c r="C112" s="47"/>
@@ -7641,12 +7730,12 @@
         <v>197</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="60">
       <c r="A113" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B113" s="46"/>
       <c r="C113" s="47"/>
@@ -7658,15 +7747,15 @@
         <v>156</v>
       </c>
       <c r="J113" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B114" s="46"/>
       <c r="C114" s="47">
@@ -7679,27 +7768,27 @@
         <v>216</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G114" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H114" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H114" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I114" s="37" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J114" s="48" t="s">
         <v>183</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B115" s="46"/>
       <c r="C115" s="47">
@@ -7712,27 +7801,27 @@
         <v>216</v>
       </c>
       <c r="F115" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="H115" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H115" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I115" s="37" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="J115" s="48" t="s">
         <v>181</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B116" s="46"/>
       <c r="C116" s="47">
@@ -7745,27 +7834,27 @@
         <v>216</v>
       </c>
       <c r="F116" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G116" s="1" t="s">
+      <c r="H116" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I116" s="37" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="J116" s="48" t="s">
         <v>179</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="75">
       <c r="A117" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B117" s="46"/>
       <c r="C117" s="47"/>
@@ -7782,12 +7871,12 @@
         <v>197</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="60">
       <c r="A118" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B118" s="46"/>
       <c r="C118" s="47"/>
@@ -7799,15 +7888,15 @@
         <v>156</v>
       </c>
       <c r="J118" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B119" s="46"/>
       <c r="C119" s="47">
@@ -7820,27 +7909,27 @@
         <v>216</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G119" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H119" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H119" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I119" s="37" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="J119" s="48" t="s">
         <v>183</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B120" s="46"/>
       <c r="C120" s="47">
@@ -7853,27 +7942,27 @@
         <v>216</v>
       </c>
       <c r="F120" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G120" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G120" s="1" t="s">
+      <c r="H120" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I120" s="37" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="J120" s="48" t="s">
         <v>181</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B121" s="46"/>
       <c r="C121" s="47">
@@ -7886,27 +7975,27 @@
         <v>216</v>
       </c>
       <c r="F121" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G121" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G121" s="1" t="s">
+      <c r="H121" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I121" s="37" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="J121" s="48" t="s">
         <v>179</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="75">
       <c r="A122" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B122" s="46"/>
       <c r="C122" s="47"/>
@@ -7923,12 +8012,12 @@
         <v>197</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="60">
       <c r="A123" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B123" s="46"/>
       <c r="C123" s="47"/>
@@ -7940,15 +8029,15 @@
         <v>156</v>
       </c>
       <c r="J123" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B124" s="46"/>
       <c r="C124" s="47">
@@ -7961,27 +8050,27 @@
         <v>216</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G124" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H124" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H124" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I124" s="37" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="J124" s="48" t="s">
         <v>183</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B125" s="46"/>
       <c r="C125" s="47">
@@ -7994,27 +8083,27 @@
         <v>216</v>
       </c>
       <c r="F125" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G125" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G125" s="1" t="s">
+      <c r="H125" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H125" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I125" s="37" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="J125" s="48" t="s">
         <v>181</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B126" s="46"/>
       <c r="C126" s="47">
@@ -8027,27 +8116,27 @@
         <v>216</v>
       </c>
       <c r="F126" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G126" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G126" s="1" t="s">
+      <c r="H126" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H126" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I126" s="37" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="J126" s="48" t="s">
         <v>179</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="75">
       <c r="A127" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B127" s="46"/>
       <c r="C127" s="47"/>
@@ -8064,86 +8153,212 @@
         <v>197</v>
       </c>
       <c r="K127" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="60">
+      <c r="A128" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B128" s="46"/>
+      <c r="C128" s="47"/>
+      <c r="D128" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" s="37"/>
+      <c r="I128" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="J128" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B129" s="46"/>
+      <c r="C129" s="47">
+        <v>3</v>
+      </c>
+      <c r="D129" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E129" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I129" s="37" t="s">
+        <v>656</v>
+      </c>
+      <c r="J129" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B130" s="46"/>
+      <c r="C130" s="47">
+        <v>4</v>
+      </c>
+      <c r="D130" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="E130" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I130" s="37" t="s">
+        <v>657</v>
+      </c>
+      <c r="J130" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B131" s="46"/>
+      <c r="C131" s="47">
+        <v>15</v>
+      </c>
+      <c r="D131" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="E131" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I131" s="37" t="s">
+        <v>658</v>
+      </c>
+      <c r="J131" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="75">
+      <c r="A132" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B132" s="46"/>
+      <c r="C132" s="47"/>
+      <c r="D132" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E132" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="I132" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="J132" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="60">
+      <c r="A133" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J133" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="K133" s="1" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="60">
-      <c r="A128" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D128" s="1" t="s">
+    <row r="134" spans="1:11">
+      <c r="A134" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I128" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J128" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="K128" s="1" t="s">
+      <c r="I134" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K134" s="1" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
-      <c r="A129" s="1" t="s">
+    <row r="135" spans="1:11">
+      <c r="A135" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K129" s="1" t="s">
+      <c r="C135" s="28">
+        <v>1</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="J135" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K135" s="1" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="130" spans="1:11">
-      <c r="A130" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C130" s="28">
-        <v>1</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="J130" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="223" spans="5:5">
-      <c r="E223" s="36"/>
-    </row>
-    <row r="224" spans="5:5">
-      <c r="E224" s="36"/>
-    </row>
-    <row r="225" spans="5:5">
-      <c r="E225" s="36"/>
-    </row>
-    <row r="226" spans="5:5">
-      <c r="E226" s="36"/>
-    </row>
-    <row r="227" spans="5:5">
-      <c r="E227" s="36"/>
     </row>
     <row r="228" spans="5:5">
       <c r="E228" s="36"/>
@@ -8151,42 +8366,37 @@
     <row r="229" spans="5:5">
       <c r="E229" s="36"/>
     </row>
-    <row r="239" spans="5:5">
-      <c r="E239" s="36"/>
-    </row>
-    <row r="241" spans="5:10">
-      <c r="E241" s="36"/>
-      <c r="J241" s="44"/>
-    </row>
-    <row r="242" spans="5:10">
-      <c r="J242" s="44"/>
-    </row>
-    <row r="243" spans="5:10">
-      <c r="E243" s="37"/>
-      <c r="J243" s="44"/>
+    <row r="230" spans="5:5">
+      <c r="E230" s="36"/>
+    </row>
+    <row r="231" spans="5:5">
+      <c r="E231" s="36"/>
+    </row>
+    <row r="232" spans="5:5">
+      <c r="E232" s="36"/>
+    </row>
+    <row r="233" spans="5:5">
+      <c r="E233" s="36"/>
+    </row>
+    <row r="234" spans="5:5">
+      <c r="E234" s="36"/>
     </row>
     <row r="244" spans="5:10">
       <c r="E244" s="36"/>
-      <c r="J244" s="44"/>
-    </row>
-    <row r="245" spans="5:10">
-      <c r="E245" s="36"/>
-      <c r="J245" s="44"/>
     </row>
     <row r="246" spans="5:10">
       <c r="E246" s="36"/>
       <c r="J246" s="44"/>
     </row>
     <row r="247" spans="5:10">
-      <c r="E247" s="36"/>
       <c r="J247" s="44"/>
     </row>
     <row r="248" spans="5:10">
-      <c r="E248" s="36"/>
+      <c r="E248" s="37"/>
       <c r="J248" s="44"/>
     </row>
     <row r="249" spans="5:10">
-      <c r="E249" s="38"/>
+      <c r="E249" s="36"/>
       <c r="J249" s="44"/>
     </row>
     <row r="250" spans="5:10">
@@ -8206,7 +8416,7 @@
       <c r="J253" s="44"/>
     </row>
     <row r="254" spans="5:10">
-      <c r="E254" s="36"/>
+      <c r="E254" s="38"/>
       <c r="J254" s="44"/>
     </row>
     <row r="255" spans="5:10">
@@ -8345,23 +8555,28 @@
       <c r="E288" s="36"/>
       <c r="J288" s="44"/>
     </row>
-    <row r="296" spans="5:5">
-      <c r="E296" s="36"/>
-    </row>
-    <row r="305" spans="10:10">
-      <c r="J305" s="44"/>
-    </row>
-    <row r="306" spans="10:10">
-      <c r="J306" s="44"/>
-    </row>
-    <row r="307" spans="10:10">
-      <c r="J307" s="44"/>
-    </row>
-    <row r="308" spans="10:10">
-      <c r="J308" s="44"/>
-    </row>
-    <row r="309" spans="10:10">
-      <c r="J309" s="44"/>
+    <row r="289" spans="5:10">
+      <c r="E289" s="36"/>
+      <c r="J289" s="44"/>
+    </row>
+    <row r="290" spans="5:10">
+      <c r="E290" s="36"/>
+      <c r="J290" s="44"/>
+    </row>
+    <row r="291" spans="5:10">
+      <c r="E291" s="36"/>
+      <c r="J291" s="44"/>
+    </row>
+    <row r="292" spans="5:10">
+      <c r="E292" s="36"/>
+      <c r="J292" s="44"/>
+    </row>
+    <row r="293" spans="5:10">
+      <c r="E293" s="36"/>
+      <c r="J293" s="44"/>
+    </row>
+    <row r="301" spans="5:10">
+      <c r="E301" s="36"/>
     </row>
     <row r="310" spans="10:10">
       <c r="J310" s="44"/>
@@ -8390,17 +8605,23 @@
     <row r="318" spans="10:10">
       <c r="J318" s="44"/>
     </row>
-    <row r="348" spans="5:5">
-      <c r="E348" s="36"/>
-    </row>
-    <row r="367" spans="5:5">
-      <c r="E367" s="36"/>
-    </row>
-    <row r="368" spans="5:5">
-      <c r="E368" s="36"/>
-    </row>
-    <row r="371" spans="5:5">
-      <c r="E371" s="36"/>
+    <row r="319" spans="10:10">
+      <c r="J319" s="44"/>
+    </row>
+    <row r="320" spans="10:10">
+      <c r="J320" s="44"/>
+    </row>
+    <row r="321" spans="10:10">
+      <c r="J321" s="44"/>
+    </row>
+    <row r="322" spans="10:10">
+      <c r="J322" s="44"/>
+    </row>
+    <row r="323" spans="10:10">
+      <c r="J323" s="44"/>
+    </row>
+    <row r="353" spans="5:5">
+      <c r="E353" s="36"/>
     </row>
     <row r="372" spans="5:5">
       <c r="E372" s="36"/>
@@ -8408,29 +8629,23 @@
     <row r="373" spans="5:5">
       <c r="E373" s="36"/>
     </row>
-    <row r="374" spans="5:5">
-      <c r="E374" s="36"/>
-    </row>
-    <row r="375" spans="5:5">
-      <c r="E375" s="36"/>
-    </row>
     <row r="376" spans="5:5">
       <c r="E376" s="36"/>
     </row>
-    <row r="382" spans="5:5">
-      <c r="E382" s="36"/>
-    </row>
-    <row r="383" spans="5:5">
-      <c r="E383" s="36"/>
-    </row>
-    <row r="384" spans="5:5">
-      <c r="E384" s="36"/>
-    </row>
-    <row r="385" spans="5:5">
-      <c r="E385" s="36"/>
-    </row>
-    <row r="386" spans="5:5">
-      <c r="E386" s="36"/>
+    <row r="377" spans="5:5">
+      <c r="E377" s="36"/>
+    </row>
+    <row r="378" spans="5:5">
+      <c r="E378" s="36"/>
+    </row>
+    <row r="379" spans="5:5">
+      <c r="E379" s="36"/>
+    </row>
+    <row r="380" spans="5:5">
+      <c r="E380" s="36"/>
+    </row>
+    <row r="381" spans="5:5">
+      <c r="E381" s="36"/>
     </row>
     <row r="387" spans="5:5">
       <c r="E387" s="36"/>
@@ -8438,6 +8653,9 @@
     <row r="388" spans="5:5">
       <c r="E388" s="36"/>
     </row>
+    <row r="389" spans="5:5">
+      <c r="E389" s="36"/>
+    </row>
     <row r="390" spans="5:5">
       <c r="E390" s="36"/>
     </row>
@@ -8450,81 +8668,80 @@
     <row r="393" spans="5:5">
       <c r="E393" s="36"/>
     </row>
+    <row r="395" spans="5:5">
+      <c r="E395" s="36"/>
+    </row>
+    <row r="396" spans="5:5">
+      <c r="E396" s="36"/>
+    </row>
     <row r="397" spans="5:5">
       <c r="E397" s="36"/>
     </row>
-    <row r="404" spans="5:5">
-      <c r="E404" s="36"/>
-    </row>
-    <row r="408" spans="5:5">
-      <c r="E408" s="36"/>
-    </row>
-    <row r="419" spans="5:10">
-      <c r="E419" s="36"/>
-    </row>
-    <row r="429" spans="5:10">
-      <c r="E429" s="36"/>
-    </row>
-    <row r="431" spans="5:10">
-      <c r="J431" s="44"/>
-    </row>
-    <row r="432" spans="5:10">
-      <c r="J432" s="44"/>
-    </row>
-    <row r="433" spans="10:10">
-      <c r="J433" s="44"/>
-    </row>
-    <row r="434" spans="10:10">
-      <c r="J434" s="44"/>
-    </row>
-    <row r="435" spans="10:10">
-      <c r="J435" s="44"/>
-    </row>
-    <row r="436" spans="10:10">
+    <row r="398" spans="5:5">
+      <c r="E398" s="36"/>
+    </row>
+    <row r="402" spans="5:5">
+      <c r="E402" s="36"/>
+    </row>
+    <row r="409" spans="5:5">
+      <c r="E409" s="36"/>
+    </row>
+    <row r="413" spans="5:5">
+      <c r="E413" s="36"/>
+    </row>
+    <row r="424" spans="5:5">
+      <c r="E424" s="36"/>
+    </row>
+    <row r="434" spans="5:10">
+      <c r="E434" s="36"/>
+    </row>
+    <row r="436" spans="5:10">
       <c r="J436" s="44"/>
     </row>
-    <row r="437" spans="10:10">
+    <row r="437" spans="5:10">
       <c r="J437" s="44"/>
     </row>
-    <row r="438" spans="10:10">
+    <row r="438" spans="5:10">
       <c r="J438" s="44"/>
     </row>
-    <row r="439" spans="10:10">
+    <row r="439" spans="5:10">
       <c r="J439" s="44"/>
     </row>
-    <row r="440" spans="10:10">
+    <row r="440" spans="5:10">
       <c r="J440" s="44"/>
     </row>
-    <row r="441" spans="10:10">
+    <row r="441" spans="5:10">
       <c r="J441" s="44"/>
     </row>
-    <row r="442" spans="10:10">
+    <row r="442" spans="5:10">
       <c r="J442" s="44"/>
     </row>
-    <row r="443" spans="10:10">
+    <row r="443" spans="5:10">
       <c r="J443" s="44"/>
     </row>
-    <row r="444" spans="10:10">
+    <row r="444" spans="5:10">
       <c r="J444" s="44"/>
     </row>
-    <row r="445" spans="10:10">
+    <row r="445" spans="5:10">
       <c r="J445" s="44"/>
     </row>
-    <row r="446" spans="10:10">
+    <row r="446" spans="5:10">
       <c r="J446" s="44"/>
     </row>
-    <row r="447" spans="10:10">
+    <row r="447" spans="5:10">
       <c r="J447" s="44"/>
     </row>
-    <row r="448" spans="10:10">
+    <row r="448" spans="5:10">
       <c r="J448" s="44"/>
     </row>
     <row r="449" spans="5:10">
       <c r="J449" s="44"/>
     </row>
     <row r="450" spans="5:10">
-      <c r="E450" s="36"/>
       <c r="J450" s="44"/>
+    </row>
+    <row r="451" spans="5:10">
+      <c r="J451" s="44"/>
     </row>
     <row r="452" spans="5:10">
       <c r="J452" s="44"/>
@@ -8536,10 +8753,8 @@
       <c r="J454" s="44"/>
     </row>
     <row r="455" spans="5:10">
+      <c r="E455" s="36"/>
       <c r="J455" s="44"/>
-    </row>
-    <row r="456" spans="5:10">
-      <c r="J456" s="44"/>
     </row>
     <row r="457" spans="5:10">
       <c r="J457" s="44"/>
@@ -8548,7 +8763,6 @@
       <c r="J458" s="44"/>
     </row>
     <row r="459" spans="5:10">
-      <c r="E459" s="36"/>
       <c r="J459" s="44"/>
     </row>
     <row r="460" spans="5:10">
@@ -8564,6 +8778,7 @@
       <c r="J463" s="44"/>
     </row>
     <row r="464" spans="5:10">
+      <c r="E464" s="36"/>
       <c r="J464" s="44"/>
     </row>
     <row r="465" spans="5:10">
@@ -8573,8 +8788,10 @@
       <c r="J466" s="44"/>
     </row>
     <row r="467" spans="5:10">
-      <c r="E467" s="36"/>
       <c r="J467" s="44"/>
+    </row>
+    <row r="468" spans="5:10">
+      <c r="J468" s="44"/>
     </row>
     <row r="469" spans="5:10">
       <c r="J469" s="44"/>
@@ -8586,10 +8803,8 @@
       <c r="J471" s="44"/>
     </row>
     <row r="472" spans="5:10">
+      <c r="E472" s="36"/>
       <c r="J472" s="44"/>
-    </row>
-    <row r="473" spans="5:10">
-      <c r="J473" s="44"/>
     </row>
     <row r="474" spans="5:10">
       <c r="J474" s="44"/>
@@ -8598,7 +8813,6 @@
       <c r="J475" s="44"/>
     </row>
     <row r="476" spans="5:10">
-      <c r="E476" s="36"/>
       <c r="J476" s="44"/>
     </row>
     <row r="477" spans="5:10">
@@ -8614,6 +8828,7 @@
       <c r="J480" s="44"/>
     </row>
     <row r="481" spans="5:10">
+      <c r="E481" s="36"/>
       <c r="J481" s="44"/>
     </row>
     <row r="482" spans="5:10">
@@ -8623,48 +8838,48 @@
       <c r="J483" s="44"/>
     </row>
     <row r="484" spans="5:10">
-      <c r="E484" s="36"/>
       <c r="J484" s="44"/>
     </row>
-    <row r="492" spans="5:10">
-      <c r="E492" s="36"/>
-    </row>
-    <row r="499" spans="5:5">
-      <c r="E499" s="36"/>
-    </row>
-    <row r="515" spans="5:5">
-      <c r="E515" s="37"/>
-    </row>
-    <row r="516" spans="5:5">
-      <c r="E516" s="37"/>
-    </row>
-    <row r="519" spans="5:5">
-      <c r="E519" s="37"/>
+    <row r="485" spans="5:10">
+      <c r="J485" s="44"/>
+    </row>
+    <row r="486" spans="5:10">
+      <c r="J486" s="44"/>
+    </row>
+    <row r="487" spans="5:10">
+      <c r="J487" s="44"/>
+    </row>
+    <row r="488" spans="5:10">
+      <c r="J488" s="44"/>
+    </row>
+    <row r="489" spans="5:10">
+      <c r="E489" s="36"/>
+      <c r="J489" s="44"/>
+    </row>
+    <row r="497" spans="5:5">
+      <c r="E497" s="36"/>
+    </row>
+    <row r="504" spans="5:5">
+      <c r="E504" s="36"/>
     </row>
     <row r="520" spans="5:5">
-      <c r="E520" s="36"/>
-    </row>
-    <row r="533" spans="5:5">
-      <c r="E533" s="36"/>
-    </row>
-    <row r="545" spans="5:5">
-      <c r="E545" s="36"/>
-    </row>
-    <row r="549" spans="5:5">
-      <c r="E549" s="36"/>
+      <c r="E520" s="37"/>
+    </row>
+    <row r="521" spans="5:5">
+      <c r="E521" s="37"/>
+    </row>
+    <row r="524" spans="5:5">
+      <c r="E524" s="37"/>
+    </row>
+    <row r="525" spans="5:5">
+      <c r="E525" s="36"/>
+    </row>
+    <row r="538" spans="5:5">
+      <c r="E538" s="36"/>
     </row>
     <row r="550" spans="5:5">
       <c r="E550" s="36"/>
     </row>
-    <row r="551" spans="5:5">
-      <c r="E551" s="36"/>
-    </row>
-    <row r="552" spans="5:5">
-      <c r="E552" s="36"/>
-    </row>
-    <row r="553" spans="5:5">
-      <c r="E553" s="36"/>
-    </row>
     <row r="554" spans="5:5">
       <c r="E554" s="36"/>
     </row>
@@ -8686,56 +8901,56 @@
     <row r="560" spans="5:5">
       <c r="E560" s="36"/>
     </row>
-    <row r="561" spans="5:10">
+    <row r="561" spans="5:5">
       <c r="E561" s="36"/>
     </row>
-    <row r="562" spans="5:10">
+    <row r="562" spans="5:5">
       <c r="E562" s="36"/>
     </row>
-    <row r="563" spans="5:10">
+    <row r="563" spans="5:5">
       <c r="E563" s="36"/>
     </row>
-    <row r="564" spans="5:10">
+    <row r="564" spans="5:5">
       <c r="E564" s="36"/>
     </row>
-    <row r="565" spans="5:10">
+    <row r="565" spans="5:5">
       <c r="E565" s="36"/>
     </row>
-    <row r="566" spans="5:10">
+    <row r="566" spans="5:5">
       <c r="E566" s="36"/>
     </row>
-    <row r="567" spans="5:10">
+    <row r="567" spans="5:5">
       <c r="E567" s="36"/>
     </row>
-    <row r="568" spans="5:10">
+    <row r="568" spans="5:5">
       <c r="E568" s="36"/>
     </row>
-    <row r="569" spans="5:10">
+    <row r="569" spans="5:5">
       <c r="E569" s="36"/>
     </row>
-    <row r="570" spans="5:10">
+    <row r="570" spans="5:5">
       <c r="E570" s="36"/>
     </row>
-    <row r="571" spans="5:10">
+    <row r="571" spans="5:5">
       <c r="E571" s="36"/>
     </row>
-    <row r="572" spans="5:10">
+    <row r="572" spans="5:5">
       <c r="E572" s="36"/>
     </row>
-    <row r="574" spans="5:10">
-      <c r="J574" s="44"/>
-    </row>
-    <row r="575" spans="5:10">
-      <c r="J575" s="44"/>
-    </row>
-    <row r="576" spans="5:10">
-      <c r="J576" s="44"/>
+    <row r="573" spans="5:5">
+      <c r="E573" s="36"/>
+    </row>
+    <row r="574" spans="5:5">
+      <c r="E574" s="36"/>
+    </row>
+    <row r="575" spans="5:5">
+      <c r="E575" s="36"/>
+    </row>
+    <row r="576" spans="5:5">
+      <c r="E576" s="36"/>
     </row>
     <row r="577" spans="5:10">
-      <c r="J577" s="44"/>
-    </row>
-    <row r="578" spans="5:10">
-      <c r="J578" s="44"/>
+      <c r="E577" s="36"/>
     </row>
     <row r="579" spans="5:10">
       <c r="J579" s="44"/>
@@ -8762,23 +8977,23 @@
       <c r="J586" s="44"/>
     </row>
     <row r="587" spans="5:10">
-      <c r="E587" s="36"/>
       <c r="J587" s="44"/>
     </row>
+    <row r="588" spans="5:10">
+      <c r="J588" s="44"/>
+    </row>
     <row r="589" spans="5:10">
-      <c r="E589" s="36"/>
+      <c r="J589" s="44"/>
     </row>
     <row r="590" spans="5:10">
-      <c r="E590" s="36"/>
+      <c r="J590" s="44"/>
     </row>
     <row r="591" spans="5:10">
-      <c r="E591" s="36"/>
+      <c r="J591" s="44"/>
     </row>
     <row r="592" spans="5:10">
       <c r="E592" s="36"/>
-    </row>
-    <row r="593" spans="5:5">
-      <c r="E593" s="36"/>
+      <c r="J592" s="44"/>
     </row>
     <row r="594" spans="5:5">
       <c r="E594" s="36"/>
@@ -8873,61 +9088,56 @@
     <row r="624" spans="5:5">
       <c r="E624" s="36"/>
     </row>
-    <row r="625" spans="5:10">
+    <row r="625" spans="5:5">
       <c r="E625" s="36"/>
     </row>
-    <row r="626" spans="5:10">
+    <row r="626" spans="5:5">
       <c r="E626" s="36"/>
     </row>
-    <row r="627" spans="5:10">
+    <row r="627" spans="5:5">
       <c r="E627" s="36"/>
     </row>
-    <row r="628" spans="5:10">
+    <row r="628" spans="5:5">
       <c r="E628" s="36"/>
     </row>
-    <row r="629" spans="5:10">
+    <row r="629" spans="5:5">
       <c r="E629" s="36"/>
     </row>
-    <row r="630" spans="5:10">
+    <row r="630" spans="5:5">
       <c r="E630" s="36"/>
     </row>
-    <row r="631" spans="5:10">
+    <row r="631" spans="5:5">
       <c r="E631" s="36"/>
     </row>
-    <row r="632" spans="5:10">
+    <row r="632" spans="5:5">
       <c r="E632" s="36"/>
     </row>
-    <row r="633" spans="5:10">
+    <row r="633" spans="5:5">
       <c r="E633" s="36"/>
     </row>
-    <row r="634" spans="5:10">
+    <row r="634" spans="5:5">
       <c r="E634" s="36"/>
     </row>
-    <row r="635" spans="5:10">
+    <row r="635" spans="5:5">
       <c r="E635" s="36"/>
     </row>
-    <row r="636" spans="5:10">
+    <row r="636" spans="5:5">
       <c r="E636" s="36"/>
     </row>
-    <row r="638" spans="5:10">
+    <row r="637" spans="5:5">
+      <c r="E637" s="36"/>
+    </row>
+    <row r="638" spans="5:5">
       <c r="E638" s="36"/>
-      <c r="J638" s="44"/>
-    </row>
-    <row r="639" spans="5:10">
+    </row>
+    <row r="639" spans="5:5">
       <c r="E639" s="36"/>
-      <c r="J639" s="44"/>
-    </row>
-    <row r="640" spans="5:10">
+    </row>
+    <row r="640" spans="5:5">
       <c r="E640" s="36"/>
-      <c r="J640" s="44"/>
     </row>
     <row r="641" spans="5:10">
       <c r="E641" s="36"/>
-      <c r="J641" s="44"/>
-    </row>
-    <row r="642" spans="5:10">
-      <c r="E642" s="36"/>
-      <c r="J642" s="44"/>
     </row>
     <row r="643" spans="5:10">
       <c r="E643" s="36"/>
@@ -9101,23 +9311,28 @@
       <c r="E685" s="36"/>
       <c r="J685" s="44"/>
     </row>
-    <row r="695" spans="5:5">
-      <c r="E695" s="36"/>
-    </row>
-    <row r="706" spans="10:10">
-      <c r="J706" s="44"/>
-    </row>
-    <row r="707" spans="10:10">
-      <c r="J707" s="44"/>
-    </row>
-    <row r="708" spans="10:10">
-      <c r="J708" s="44"/>
-    </row>
-    <row r="709" spans="10:10">
-      <c r="J709" s="44"/>
-    </row>
-    <row r="710" spans="10:10">
-      <c r="J710" s="44"/>
+    <row r="686" spans="5:10">
+      <c r="E686" s="36"/>
+      <c r="J686" s="44"/>
+    </row>
+    <row r="687" spans="5:10">
+      <c r="E687" s="36"/>
+      <c r="J687" s="44"/>
+    </row>
+    <row r="688" spans="5:10">
+      <c r="E688" s="36"/>
+      <c r="J688" s="44"/>
+    </row>
+    <row r="689" spans="5:10">
+      <c r="E689" s="36"/>
+      <c r="J689" s="44"/>
+    </row>
+    <row r="690" spans="5:10">
+      <c r="E690" s="36"/>
+      <c r="J690" s="44"/>
+    </row>
+    <row r="700" spans="5:10">
+      <c r="E700" s="36"/>
     </row>
     <row r="711" spans="10:10">
       <c r="J711" s="44"/>
@@ -9162,31 +9377,26 @@
       <c r="J724" s="44"/>
     </row>
     <row r="725" spans="5:10">
-      <c r="E725" s="36"/>
       <c r="J725" s="44"/>
     </row>
-    <row r="735" spans="5:10">
-      <c r="E735" s="36"/>
-    </row>
-    <row r="746" spans="5:10">
-      <c r="E746" s="36"/>
-      <c r="J746" s="44"/>
-    </row>
-    <row r="747" spans="5:10">
-      <c r="E747" s="36"/>
-      <c r="J747" s="44"/>
-    </row>
-    <row r="748" spans="5:10">
-      <c r="E748" s="36"/>
-      <c r="J748" s="44"/>
-    </row>
-    <row r="749" spans="5:10">
-      <c r="E749" s="36"/>
-      <c r="J749" s="44"/>
-    </row>
-    <row r="750" spans="5:10">
-      <c r="E750" s="36"/>
-      <c r="J750" s="44"/>
+    <row r="726" spans="5:10">
+      <c r="J726" s="44"/>
+    </row>
+    <row r="727" spans="5:10">
+      <c r="J727" s="44"/>
+    </row>
+    <row r="728" spans="5:10">
+      <c r="J728" s="44"/>
+    </row>
+    <row r="729" spans="5:10">
+      <c r="J729" s="44"/>
+    </row>
+    <row r="730" spans="5:10">
+      <c r="E730" s="36"/>
+      <c r="J730" s="44"/>
+    </row>
+    <row r="740" spans="5:10">
+      <c r="E740" s="36"/>
     </row>
     <row r="751" spans="5:10">
       <c r="E751" s="36"/>
@@ -9232,6 +9442,10 @@
       <c r="E761" s="36"/>
       <c r="J761" s="44"/>
     </row>
+    <row r="762" spans="5:10">
+      <c r="E762" s="36"/>
+      <c r="J762" s="44"/>
+    </row>
     <row r="763" spans="5:10">
       <c r="E763" s="36"/>
       <c r="J763" s="44"/>
@@ -9248,10 +9462,6 @@
       <c r="E766" s="36"/>
       <c r="J766" s="44"/>
     </row>
-    <row r="767" spans="5:10">
-      <c r="E767" s="36"/>
-      <c r="J767" s="44"/>
-    </row>
     <row r="768" spans="5:10">
       <c r="E768" s="36"/>
       <c r="J768" s="44"/>
@@ -9288,20 +9498,31 @@
       <c r="E776" s="36"/>
       <c r="J776" s="44"/>
     </row>
+    <row r="777" spans="5:10">
+      <c r="E777" s="36"/>
+      <c r="J777" s="44"/>
+    </row>
+    <row r="778" spans="5:10">
+      <c r="E778" s="36"/>
+      <c r="J778" s="44"/>
+    </row>
     <row r="779" spans="5:10">
       <c r="E779" s="36"/>
-    </row>
-    <row r="783" spans="5:10">
-      <c r="E783" s="36"/>
+      <c r="J779" s="44"/>
+    </row>
+    <row r="780" spans="5:10">
+      <c r="E780" s="36"/>
+      <c r="J780" s="44"/>
+    </row>
+    <row r="781" spans="5:10">
+      <c r="E781" s="36"/>
+      <c r="J781" s="44"/>
     </row>
     <row r="784" spans="5:10">
       <c r="E784" s="36"/>
     </row>
-    <row r="785" spans="5:5">
-      <c r="E785" s="36"/>
-    </row>
-    <row r="786" spans="5:5">
-      <c r="E786" s="36"/>
+    <row r="788" spans="5:5">
+      <c r="E788" s="36"/>
     </row>
     <row r="789" spans="5:5">
       <c r="E789" s="36"/>
@@ -9312,8 +9533,8 @@
     <row r="791" spans="5:5">
       <c r="E791" s="36"/>
     </row>
-    <row r="792" spans="5:5">
-      <c r="E792" s="36"/>
+    <row r="794" spans="5:5">
+      <c r="E794" s="36"/>
     </row>
     <row r="795" spans="5:5">
       <c r="E795" s="36"/>
@@ -9324,12 +9545,6 @@
     <row r="797" spans="5:5">
       <c r="E797" s="36"/>
     </row>
-    <row r="798" spans="5:5">
-      <c r="E798" s="36"/>
-    </row>
-    <row r="799" spans="5:5">
-      <c r="E799" s="36"/>
-    </row>
     <row r="800" spans="5:5">
       <c r="E800" s="36"/>
     </row>
@@ -9357,6 +9572,9 @@
     <row r="808" spans="5:5">
       <c r="E808" s="36"/>
     </row>
+    <row r="809" spans="5:5">
+      <c r="E809" s="36"/>
+    </row>
     <row r="810" spans="5:5">
       <c r="E810" s="36"/>
     </row>
@@ -9369,9 +9587,6 @@
     <row r="813" spans="5:5">
       <c r="E813" s="36"/>
     </row>
-    <row r="814" spans="5:5">
-      <c r="E814" s="36"/>
-    </row>
     <row r="815" spans="5:5">
       <c r="E815" s="36"/>
     </row>
@@ -9399,6 +9614,9 @@
     <row r="823" spans="5:5">
       <c r="E823" s="36"/>
     </row>
+    <row r="824" spans="5:5">
+      <c r="E824" s="36"/>
+    </row>
     <row r="825" spans="5:5">
       <c r="E825" s="36"/>
     </row>
@@ -9411,9 +9629,6 @@
     <row r="828" spans="5:5">
       <c r="E828" s="36"/>
     </row>
-    <row r="829" spans="5:5">
-      <c r="E829" s="36"/>
-    </row>
     <row r="830" spans="5:5">
       <c r="E830" s="36"/>
     </row>
@@ -9441,6 +9656,9 @@
     <row r="838" spans="5:5">
       <c r="E838" s="36"/>
     </row>
+    <row r="839" spans="5:5">
+      <c r="E839" s="36"/>
+    </row>
     <row r="840" spans="5:5">
       <c r="E840" s="36"/>
     </row>
@@ -9453,9 +9671,6 @@
     <row r="843" spans="5:5">
       <c r="E843" s="36"/>
     </row>
-    <row r="844" spans="5:5">
-      <c r="E844" s="36"/>
-    </row>
     <row r="845" spans="5:5">
       <c r="E845" s="36"/>
     </row>
@@ -9525,48 +9740,48 @@
     <row r="867" spans="5:5">
       <c r="E867" s="36"/>
     </row>
+    <row r="868" spans="5:5">
+      <c r="E868" s="36"/>
+    </row>
     <row r="869" spans="5:5">
       <c r="E869" s="36"/>
     </row>
-    <row r="882" spans="5:5">
-      <c r="E882" s="36"/>
-    </row>
-    <row r="896" spans="5:5">
-      <c r="E896" s="36"/>
-    </row>
-    <row r="898" spans="5:5">
-      <c r="E898" s="36"/>
-    </row>
-    <row r="911" spans="5:5">
-      <c r="E911" s="36"/>
-    </row>
-    <row r="925" spans="5:5">
-      <c r="E925" s="36"/>
-    </row>
-    <row r="927" spans="5:5">
-      <c r="E927" s="36"/>
-    </row>
-    <row r="940" spans="5:5">
-      <c r="E940" s="36"/>
-    </row>
-    <row r="954" spans="5:5">
-      <c r="E954" s="36"/>
-    </row>
-    <row r="957" spans="5:5">
-      <c r="E957" s="36"/>
-    </row>
-    <row r="958" spans="5:5">
-      <c r="E958" s="36"/>
+    <row r="870" spans="5:5">
+      <c r="E870" s="36"/>
+    </row>
+    <row r="871" spans="5:5">
+      <c r="E871" s="36"/>
+    </row>
+    <row r="872" spans="5:5">
+      <c r="E872" s="36"/>
+    </row>
+    <row r="874" spans="5:5">
+      <c r="E874" s="36"/>
+    </row>
+    <row r="887" spans="5:5">
+      <c r="E887" s="36"/>
+    </row>
+    <row r="901" spans="5:5">
+      <c r="E901" s="36"/>
+    </row>
+    <row r="903" spans="5:5">
+      <c r="E903" s="36"/>
+    </row>
+    <row r="916" spans="5:5">
+      <c r="E916" s="36"/>
+    </row>
+    <row r="930" spans="5:5">
+      <c r="E930" s="36"/>
+    </row>
+    <row r="932" spans="5:5">
+      <c r="E932" s="36"/>
+    </row>
+    <row r="945" spans="5:5">
+      <c r="E945" s="36"/>
     </row>
     <row r="959" spans="5:5">
       <c r="E959" s="36"/>
     </row>
-    <row r="960" spans="5:5">
-      <c r="E960" s="36"/>
-    </row>
-    <row r="961" spans="5:5">
-      <c r="E961" s="36"/>
-    </row>
     <row r="962" spans="5:5">
       <c r="E962" s="36"/>
     </row>
@@ -9594,82 +9809,82 @@
     <row r="970" spans="5:5">
       <c r="E970" s="36"/>
     </row>
-    <row r="979" spans="5:8">
-      <c r="E979" s="36"/>
-    </row>
-    <row r="990" spans="5:8">
-      <c r="F990" s="36"/>
-      <c r="H990" s="36"/>
-    </row>
-    <row r="991" spans="5:8">
-      <c r="F991" s="36"/>
-    </row>
-    <row r="992" spans="5:8">
-      <c r="F992" s="36"/>
-      <c r="H992" s="36"/>
-    </row>
-    <row r="996" spans="5:5">
-      <c r="E996" s="36"/>
-    </row>
-    <row r="1013" spans="5:5">
-      <c r="E1013" s="36"/>
-    </row>
-    <row r="1030" spans="5:5">
-      <c r="E1030" s="36"/>
-    </row>
-    <row r="1047" spans="5:5">
-      <c r="E1047" s="36"/>
-    </row>
-    <row r="1061" spans="5:8">
-      <c r="H1061" s="49"/>
-    </row>
-    <row r="1064" spans="5:8">
-      <c r="E1064" s="36"/>
-    </row>
-    <row r="1081" spans="5:5">
-      <c r="E1081" s="36"/>
-    </row>
-    <row r="1098" spans="5:5">
-      <c r="E1098" s="36"/>
-    </row>
-    <row r="1115" spans="5:5">
-      <c r="E1115" s="36"/>
-    </row>
-    <row r="1132" spans="5:5">
-      <c r="E1132" s="36"/>
-    </row>
-    <row r="1149" spans="5:5">
-      <c r="E1149" s="36"/>
-    </row>
-    <row r="1166" spans="5:5">
-      <c r="E1166" s="36"/>
-    </row>
-    <row r="1183" spans="5:5">
-      <c r="E1183" s="36"/>
-    </row>
-    <row r="1200" spans="5:5">
-      <c r="E1200" s="36"/>
-    </row>
-    <row r="1217" spans="5:5">
-      <c r="E1217" s="36"/>
-    </row>
-    <row r="1234" spans="5:10">
-      <c r="E1234" s="36"/>
-    </row>
-    <row r="1244" spans="5:10">
-      <c r="J1244" s="44"/>
-    </row>
-    <row r="1245" spans="5:10">
-      <c r="J1245" s="44"/>
-    </row>
-    <row r="1246" spans="5:10">
-      <c r="J1246" s="44"/>
-    </row>
-    <row r="1247" spans="5:10">
-      <c r="J1247" s="44"/>
-    </row>
-    <row r="1248" spans="5:10">
-      <c r="J1248" s="44"/>
+    <row r="971" spans="5:5">
+      <c r="E971" s="36"/>
+    </row>
+    <row r="972" spans="5:5">
+      <c r="E972" s="36"/>
+    </row>
+    <row r="973" spans="5:5">
+      <c r="E973" s="36"/>
+    </row>
+    <row r="974" spans="5:5">
+      <c r="E974" s="36"/>
+    </row>
+    <row r="975" spans="5:5">
+      <c r="E975" s="36"/>
+    </row>
+    <row r="984" spans="5:5">
+      <c r="E984" s="36"/>
+    </row>
+    <row r="995" spans="5:8">
+      <c r="F995" s="36"/>
+      <c r="H995" s="36"/>
+    </row>
+    <row r="996" spans="5:8">
+      <c r="F996" s="36"/>
+    </row>
+    <row r="997" spans="5:8">
+      <c r="F997" s="36"/>
+      <c r="H997" s="36"/>
+    </row>
+    <row r="1001" spans="5:8">
+      <c r="E1001" s="36"/>
+    </row>
+    <row r="1018" spans="5:5">
+      <c r="E1018" s="36"/>
+    </row>
+    <row r="1035" spans="5:5">
+      <c r="E1035" s="36"/>
+    </row>
+    <row r="1052" spans="5:5">
+      <c r="E1052" s="36"/>
+    </row>
+    <row r="1066" spans="5:8">
+      <c r="H1066" s="49"/>
+    </row>
+    <row r="1069" spans="5:8">
+      <c r="E1069" s="36"/>
+    </row>
+    <row r="1086" spans="5:5">
+      <c r="E1086" s="36"/>
+    </row>
+    <row r="1103" spans="5:5">
+      <c r="E1103" s="36"/>
+    </row>
+    <row r="1120" spans="5:5">
+      <c r="E1120" s="36"/>
+    </row>
+    <row r="1137" spans="5:5">
+      <c r="E1137" s="36"/>
+    </row>
+    <row r="1154" spans="5:5">
+      <c r="E1154" s="36"/>
+    </row>
+    <row r="1171" spans="5:5">
+      <c r="E1171" s="36"/>
+    </row>
+    <row r="1188" spans="5:5">
+      <c r="E1188" s="36"/>
+    </row>
+    <row r="1205" spans="5:5">
+      <c r="E1205" s="36"/>
+    </row>
+    <row r="1222" spans="5:5">
+      <c r="E1222" s="36"/>
+    </row>
+    <row r="1239" spans="5:5">
+      <c r="E1239" s="36"/>
     </row>
     <row r="1249" spans="5:10">
       <c r="J1249" s="44"/>
@@ -9696,115 +9911,110 @@
       <c r="J1256" s="44"/>
     </row>
     <row r="1257" spans="5:10">
-      <c r="E1257" s="36"/>
       <c r="J1257" s="44"/>
     </row>
-    <row r="1278" spans="5:5">
-      <c r="E1278" s="36"/>
-    </row>
-    <row r="1293" spans="5:5">
-      <c r="E1293" s="36"/>
-    </row>
-    <row r="1308" spans="5:5">
-      <c r="E1308" s="36"/>
-    </row>
-    <row r="1323" spans="5:5">
-      <c r="E1323" s="36"/>
-    </row>
-    <row r="1339" spans="5:5">
-      <c r="E1339" s="36"/>
-    </row>
-    <row r="1347" spans="5:10">
-      <c r="E1347" s="36"/>
-    </row>
-    <row r="1356" spans="5:10">
-      <c r="J1356" s="44"/>
-    </row>
-    <row r="1357" spans="5:10">
-      <c r="J1357" s="44"/>
-    </row>
-    <row r="1358" spans="5:10">
-      <c r="J1358" s="44"/>
-    </row>
-    <row r="1359" spans="5:10">
-      <c r="J1359" s="44"/>
-    </row>
-    <row r="1360" spans="5:10">
-      <c r="J1360" s="44"/>
-    </row>
-    <row r="1361" spans="5:10">
+    <row r="1258" spans="5:10">
+      <c r="J1258" s="44"/>
+    </row>
+    <row r="1259" spans="5:10">
+      <c r="J1259" s="44"/>
+    </row>
+    <row r="1260" spans="5:10">
+      <c r="J1260" s="44"/>
+    </row>
+    <row r="1261" spans="5:10">
+      <c r="J1261" s="44"/>
+    </row>
+    <row r="1262" spans="5:10">
+      <c r="E1262" s="36"/>
+      <c r="J1262" s="44"/>
+    </row>
+    <row r="1283" spans="5:5">
+      <c r="E1283" s="36"/>
+    </row>
+    <row r="1298" spans="5:5">
+      <c r="E1298" s="36"/>
+    </row>
+    <row r="1313" spans="5:5">
+      <c r="E1313" s="36"/>
+    </row>
+    <row r="1328" spans="5:5">
+      <c r="E1328" s="36"/>
+    </row>
+    <row r="1344" spans="5:5">
+      <c r="E1344" s="36"/>
+    </row>
+    <row r="1352" spans="5:5">
+      <c r="E1352" s="36"/>
+    </row>
+    <row r="1361" spans="10:10">
       <c r="J1361" s="44"/>
     </row>
-    <row r="1362" spans="5:10">
+    <row r="1362" spans="10:10">
       <c r="J1362" s="44"/>
     </row>
-    <row r="1363" spans="5:10">
+    <row r="1363" spans="10:10">
       <c r="J1363" s="44"/>
     </row>
-    <row r="1364" spans="5:10">
+    <row r="1364" spans="10:10">
       <c r="J1364" s="44"/>
     </row>
-    <row r="1365" spans="5:10">
+    <row r="1365" spans="10:10">
       <c r="J1365" s="44"/>
     </row>
-    <row r="1366" spans="5:10">
+    <row r="1366" spans="10:10">
       <c r="J1366" s="44"/>
     </row>
-    <row r="1367" spans="5:10">
+    <row r="1367" spans="10:10">
       <c r="J1367" s="44"/>
     </row>
-    <row r="1368" spans="5:10">
+    <row r="1368" spans="10:10">
       <c r="J1368" s="44"/>
     </row>
-    <row r="1369" spans="5:10">
+    <row r="1369" spans="10:10">
       <c r="J1369" s="44"/>
     </row>
-    <row r="1370" spans="5:10">
+    <row r="1370" spans="10:10">
       <c r="J1370" s="44"/>
     </row>
-    <row r="1371" spans="5:10">
+    <row r="1371" spans="10:10">
       <c r="J1371" s="44"/>
     </row>
-    <row r="1372" spans="5:10">
+    <row r="1372" spans="10:10">
       <c r="J1372" s="44"/>
     </row>
-    <row r="1373" spans="5:10">
+    <row r="1373" spans="10:10">
       <c r="J1373" s="44"/>
     </row>
-    <row r="1374" spans="5:10">
+    <row r="1374" spans="10:10">
       <c r="J1374" s="44"/>
     </row>
-    <row r="1375" spans="5:10">
-      <c r="E1375" s="36"/>
+    <row r="1375" spans="10:10">
       <c r="J1375" s="44"/>
     </row>
-    <row r="1383" spans="5:5">
-      <c r="E1383" s="36"/>
-    </row>
-    <row r="1390" spans="5:5">
-      <c r="E1390" s="36"/>
-    </row>
-    <row r="1715" spans="6:8">
-      <c r="H1715" s="36"/>
-    </row>
-    <row r="1716" spans="6:8">
-      <c r="F1716" s="36"/>
-      <c r="H1716" s="36"/>
-    </row>
-    <row r="1717" spans="6:8">
-      <c r="F1717" s="36"/>
-      <c r="H1717" s="36"/>
-    </row>
-    <row r="1718" spans="6:8">
-      <c r="F1718" s="36"/>
-      <c r="H1718" s="36"/>
-    </row>
-    <row r="1719" spans="6:8">
-      <c r="F1719" s="36"/>
-      <c r="H1719" s="36"/>
+    <row r="1376" spans="10:10">
+      <c r="J1376" s="44"/>
+    </row>
+    <row r="1377" spans="5:10">
+      <c r="J1377" s="44"/>
+    </row>
+    <row r="1378" spans="5:10">
+      <c r="J1378" s="44"/>
+    </row>
+    <row r="1379" spans="5:10">
+      <c r="J1379" s="44"/>
+    </row>
+    <row r="1380" spans="5:10">
+      <c r="E1380" s="36"/>
+      <c r="J1380" s="44"/>
+    </row>
+    <row r="1388" spans="5:10">
+      <c r="E1388" s="36"/>
+    </row>
+    <row r="1395" spans="5:5">
+      <c r="E1395" s="36"/>
     </row>
     <row r="1720" spans="6:8">
-      <c r="F1720" s="36"/>
       <c r="H1720" s="36"/>
     </row>
     <row r="1721" spans="6:8">
@@ -9816,86 +10026,81 @@
       <c r="H1722" s="36"/>
     </row>
     <row r="1723" spans="6:8">
+      <c r="F1723" s="36"/>
       <c r="H1723" s="36"/>
     </row>
+    <row r="1724" spans="6:8">
+      <c r="F1724" s="36"/>
+      <c r="H1724" s="36"/>
+    </row>
     <row r="1725" spans="6:8">
+      <c r="F1725" s="36"/>
       <c r="H1725" s="36"/>
     </row>
+    <row r="1726" spans="6:8">
+      <c r="F1726" s="36"/>
+      <c r="H1726" s="36"/>
+    </row>
     <row r="1727" spans="6:8">
+      <c r="F1727" s="36"/>
       <c r="H1727" s="36"/>
     </row>
-    <row r="1729" spans="6:8">
-      <c r="H1729" s="36"/>
-    </row>
-    <row r="1731" spans="6:8">
-      <c r="H1731" s="36"/>
+    <row r="1728" spans="6:8">
+      <c r="H1728" s="36"/>
+    </row>
+    <row r="1730" spans="6:8">
+      <c r="H1730" s="36"/>
     </row>
     <row r="1732" spans="6:8">
-      <c r="F1732" s="36"/>
       <c r="H1732" s="36"/>
     </row>
-    <row r="1733" spans="6:8">
-      <c r="H1733" s="36"/>
-    </row>
     <row r="1734" spans="6:8">
-      <c r="F1734" s="36"/>
-      <c r="H1734" s="38"/>
-    </row>
-    <row r="1735" spans="6:8">
-      <c r="H1735" s="36"/>
+      <c r="H1734" s="36"/>
     </row>
     <row r="1736" spans="6:8">
-      <c r="F1736" s="37"/>
-      <c r="H1736" s="38"/>
+      <c r="H1736" s="36"/>
     </row>
     <row r="1737" spans="6:8">
       <c r="F1737" s="36"/>
       <c r="H1737" s="36"/>
     </row>
     <row r="1738" spans="6:8">
-      <c r="F1738" s="36"/>
-      <c r="H1738" s="38"/>
+      <c r="H1738" s="36"/>
     </row>
     <row r="1739" spans="6:8">
       <c r="F1739" s="36"/>
-      <c r="H1739" s="36"/>
+      <c r="H1739" s="38"/>
     </row>
     <row r="1740" spans="6:8">
-      <c r="F1740" s="36"/>
-      <c r="H1740" s="38"/>
+      <c r="H1740" s="36"/>
     </row>
     <row r="1741" spans="6:8">
-      <c r="F1741" s="36"/>
-      <c r="H1741" s="36"/>
+      <c r="F1741" s="37"/>
+      <c r="H1741" s="38"/>
     </row>
     <row r="1742" spans="6:8">
-      <c r="F1742" s="38"/>
-      <c r="H1742" s="38"/>
+      <c r="F1742" s="36"/>
+      <c r="H1742" s="36"/>
     </row>
     <row r="1743" spans="6:8">
       <c r="F1743" s="36"/>
-      <c r="G1743" s="36"/>
-      <c r="H1743" s="36"/>
+      <c r="H1743" s="38"/>
     </row>
     <row r="1744" spans="6:8">
       <c r="F1744" s="36"/>
-      <c r="G1744" s="36"/>
       <c r="H1744" s="36"/>
     </row>
     <row r="1745" spans="6:8">
       <c r="F1745" s="36"/>
-      <c r="G1745" s="36"/>
-      <c r="H1745" s="36"/>
+      <c r="H1745" s="38"/>
     </row>
     <row r="1746" spans="6:8">
       <c r="F1746" s="36"/>
-      <c r="G1746" s="36"/>
       <c r="H1746" s="36"/>
     </row>
     <row r="1747" spans="6:8">
-      <c r="F1747" s="36"/>
-      <c r="G1747" s="36"/>
-      <c r="H1747" s="36"/>
+      <c r="F1747" s="38"/>
+      <c r="H1747" s="38"/>
     </row>
     <row r="1748" spans="6:8">
       <c r="F1748" s="36"/>
@@ -10068,31 +10273,39 @@
       <c r="H1781" s="36"/>
     </row>
     <row r="1782" spans="6:8">
+      <c r="F1782" s="36"/>
       <c r="G1782" s="36"/>
+      <c r="H1782" s="36"/>
     </row>
     <row r="1783" spans="6:8">
       <c r="F1783" s="36"/>
       <c r="G1783" s="36"/>
+      <c r="H1783" s="36"/>
     </row>
     <row r="1784" spans="6:8">
+      <c r="F1784" s="36"/>
       <c r="G1784" s="36"/>
+      <c r="H1784" s="36"/>
     </row>
     <row r="1785" spans="6:8">
+      <c r="F1785" s="36"/>
       <c r="G1785" s="36"/>
+      <c r="H1785" s="36"/>
     </row>
     <row r="1786" spans="6:8">
+      <c r="F1786" s="36"/>
       <c r="G1786" s="36"/>
+      <c r="H1786" s="36"/>
     </row>
     <row r="1787" spans="6:8">
       <c r="G1787" s="36"/>
     </row>
     <row r="1788" spans="6:8">
+      <c r="F1788" s="36"/>
       <c r="G1788" s="36"/>
     </row>
     <row r="1789" spans="6:8">
-      <c r="F1789" s="36"/>
       <c r="G1789" s="36"/>
-      <c r="H1789" s="36"/>
     </row>
     <row r="1790" spans="6:8">
       <c r="G1790" s="36"/>
@@ -10103,47 +10316,49 @@
     <row r="1792" spans="6:8">
       <c r="G1792" s="36"/>
     </row>
-    <row r="1793" spans="7:7">
+    <row r="1793" spans="6:8">
       <c r="G1793" s="36"/>
     </row>
-    <row r="1794" spans="7:7">
+    <row r="1794" spans="6:8">
+      <c r="F1794" s="36"/>
       <c r="G1794" s="36"/>
-    </row>
-    <row r="1795" spans="7:7">
+      <c r="H1794" s="36"/>
+    </row>
+    <row r="1795" spans="6:8">
       <c r="G1795" s="36"/>
     </row>
-    <row r="1796" spans="7:7">
+    <row r="1796" spans="6:8">
       <c r="G1796" s="36"/>
     </row>
-    <row r="1797" spans="7:7">
+    <row r="1797" spans="6:8">
       <c r="G1797" s="36"/>
     </row>
-    <row r="1798" spans="7:7">
+    <row r="1798" spans="6:8">
       <c r="G1798" s="36"/>
     </row>
-    <row r="1799" spans="7:7">
+    <row r="1799" spans="6:8">
       <c r="G1799" s="36"/>
     </row>
-    <row r="1841" spans="6:6">
-      <c r="F1841" s="36"/>
-    </row>
-    <row r="1858" spans="6:8">
-      <c r="H1858" s="36"/>
-    </row>
-    <row r="1860" spans="6:8">
-      <c r="F1860" s="36"/>
-      <c r="H1860" s="36"/>
-    </row>
-    <row r="1861" spans="6:8">
-      <c r="F1861" s="36"/>
-      <c r="H1861" s="36"/>
-    </row>
-    <row r="1862" spans="6:8">
-      <c r="H1862" s="36"/>
-    </row>
-    <row r="1864" spans="6:8">
-      <c r="F1864" s="36"/>
-      <c r="H1864" s="36"/>
+    <row r="1800" spans="6:8">
+      <c r="G1800" s="36"/>
+    </row>
+    <row r="1801" spans="6:8">
+      <c r="G1801" s="36"/>
+    </row>
+    <row r="1802" spans="6:8">
+      <c r="G1802" s="36"/>
+    </row>
+    <row r="1803" spans="6:8">
+      <c r="G1803" s="36"/>
+    </row>
+    <row r="1804" spans="6:8">
+      <c r="G1804" s="36"/>
+    </row>
+    <row r="1846" spans="6:6">
+      <c r="F1846" s="36"/>
+    </row>
+    <row r="1863" spans="6:8">
+      <c r="H1863" s="36"/>
     </row>
     <row r="1865" spans="6:8">
       <c r="F1865" s="36"/>
@@ -10154,47 +10369,42 @@
       <c r="H1866" s="36"/>
     </row>
     <row r="1867" spans="6:8">
-      <c r="F1867" s="36"/>
       <c r="H1867" s="36"/>
-    </row>
-    <row r="1868" spans="6:8">
-      <c r="F1868" s="36"/>
-      <c r="H1868" s="36"/>
     </row>
     <row r="1869" spans="6:8">
       <c r="F1869" s="36"/>
       <c r="H1869" s="36"/>
     </row>
     <row r="1870" spans="6:8">
+      <c r="F1870" s="36"/>
       <c r="H1870" s="36"/>
     </row>
     <row r="1871" spans="6:8">
+      <c r="F1871" s="36"/>
       <c r="H1871" s="36"/>
     </row>
     <row r="1872" spans="6:8">
+      <c r="F1872" s="36"/>
       <c r="H1872" s="36"/>
     </row>
+    <row r="1873" spans="6:8">
+      <c r="F1873" s="36"/>
+      <c r="H1873" s="36"/>
+    </row>
     <row r="1874" spans="6:8">
+      <c r="F1874" s="36"/>
       <c r="H1874" s="36"/>
     </row>
     <row r="1875" spans="6:8">
-      <c r="F1875" s="36"/>
       <c r="H1875" s="36"/>
     </row>
     <row r="1876" spans="6:8">
-      <c r="F1876" s="36"/>
       <c r="H1876" s="36"/>
     </row>
     <row r="1877" spans="6:8">
-      <c r="F1877" s="36"/>
       <c r="H1877" s="36"/>
     </row>
-    <row r="1878" spans="6:8">
-      <c r="F1878" s="36"/>
-      <c r="H1878" s="36"/>
-    </row>
     <row r="1879" spans="6:8">
-      <c r="F1879" s="36"/>
       <c r="H1879" s="36"/>
     </row>
     <row r="1880" spans="6:8">
@@ -10206,6 +10416,7 @@
       <c r="H1881" s="36"/>
     </row>
     <row r="1882" spans="6:8">
+      <c r="F1882" s="36"/>
       <c r="H1882" s="36"/>
     </row>
     <row r="1883" spans="6:8">
@@ -10224,361 +10435,355 @@
       <c r="F1886" s="36"/>
       <c r="H1886" s="36"/>
     </row>
+    <row r="1887" spans="6:8">
+      <c r="H1887" s="36"/>
+    </row>
     <row r="1888" spans="6:8">
+      <c r="F1888" s="36"/>
       <c r="H1888" s="36"/>
+    </row>
+    <row r="1889" spans="6:8">
+      <c r="F1889" s="36"/>
+      <c r="H1889" s="36"/>
     </row>
     <row r="1890" spans="6:8">
       <c r="F1890" s="36"/>
       <c r="H1890" s="36"/>
     </row>
-    <row r="1892" spans="6:8">
-      <c r="H1892" s="36"/>
-    </row>
-    <row r="1894" spans="6:8">
-      <c r="H1894" s="36"/>
-    </row>
-    <row r="1896" spans="6:8">
-      <c r="H1896" s="36"/>
+    <row r="1891" spans="6:8">
+      <c r="F1891" s="36"/>
+      <c r="H1891" s="36"/>
+    </row>
+    <row r="1893" spans="6:8">
+      <c r="H1893" s="36"/>
+    </row>
+    <row r="1895" spans="6:8">
+      <c r="F1895" s="36"/>
+      <c r="H1895" s="36"/>
     </row>
     <row r="1897" spans="6:8">
-      <c r="F1897" s="36"/>
       <c r="H1897" s="36"/>
     </row>
-    <row r="1898" spans="6:8">
-      <c r="H1898" s="36"/>
-    </row>
-    <row r="1900" spans="6:8">
-      <c r="H1900" s="36"/>
+    <row r="1899" spans="6:8">
+      <c r="H1899" s="36"/>
     </row>
     <row r="1901" spans="6:8">
-      <c r="F1901" s="36"/>
       <c r="H1901" s="36"/>
     </row>
     <row r="1902" spans="6:8">
+      <c r="F1902" s="36"/>
       <c r="H1902" s="36"/>
     </row>
-    <row r="1904" spans="6:8">
-      <c r="H1904" s="36"/>
+    <row r="1903" spans="6:8">
+      <c r="H1903" s="36"/>
+    </row>
+    <row r="1905" spans="6:8">
+      <c r="H1905" s="36"/>
     </row>
     <row r="1906" spans="6:8">
+      <c r="F1906" s="36"/>
       <c r="H1906" s="36"/>
     </row>
-    <row r="1908" spans="6:8">
-      <c r="H1908" s="36"/>
-    </row>
-    <row r="1910" spans="6:8">
-      <c r="H1910" s="36"/>
-    </row>
-    <row r="1912" spans="6:8">
-      <c r="F1912" s="36"/>
-      <c r="H1912" s="36"/>
-    </row>
-    <row r="1922" spans="6:6">
-      <c r="F1922" s="36"/>
-    </row>
-    <row r="1939" spans="6:8">
-      <c r="H1939" s="36"/>
-    </row>
-    <row r="1941" spans="6:8">
-      <c r="H1941" s="36"/>
-    </row>
-    <row r="1943" spans="6:8">
-      <c r="F1943" s="36"/>
-      <c r="H1943" s="36"/>
-    </row>
-    <row r="1945" spans="6:8">
-      <c r="H1945" s="36"/>
-    </row>
-    <row r="1947" spans="6:8">
-      <c r="H1947" s="36"/>
-    </row>
-    <row r="1949" spans="6:8">
-      <c r="H1949" s="36"/>
-    </row>
-    <row r="1951" spans="6:8">
-      <c r="H1951" s="36"/>
+    <row r="1907" spans="6:8">
+      <c r="H1907" s="36"/>
+    </row>
+    <row r="1909" spans="6:8">
+      <c r="H1909" s="36"/>
+    </row>
+    <row r="1911" spans="6:8">
+      <c r="H1911" s="36"/>
+    </row>
+    <row r="1913" spans="6:8">
+      <c r="H1913" s="36"/>
+    </row>
+    <row r="1915" spans="6:8">
+      <c r="H1915" s="36"/>
+    </row>
+    <row r="1917" spans="6:8">
+      <c r="F1917" s="36"/>
+      <c r="H1917" s="36"/>
+    </row>
+    <row r="1927" spans="6:6">
+      <c r="F1927" s="36"/>
+    </row>
+    <row r="1944" spans="6:8">
+      <c r="H1944" s="36"/>
+    </row>
+    <row r="1946" spans="6:8">
+      <c r="H1946" s="36"/>
+    </row>
+    <row r="1948" spans="6:8">
+      <c r="F1948" s="36"/>
+      <c r="H1948" s="36"/>
+    </row>
+    <row r="1950" spans="6:8">
+      <c r="H1950" s="36"/>
     </row>
     <row r="1952" spans="6:8">
-      <c r="F1952" s="36"/>
       <c r="H1952" s="36"/>
     </row>
-    <row r="1953" spans="6:8">
-      <c r="H1953" s="36"/>
-    </row>
-    <row r="1955" spans="6:8">
-      <c r="H1955" s="36"/>
+    <row r="1954" spans="6:8">
+      <c r="H1954" s="36"/>
+    </row>
+    <row r="1956" spans="6:8">
+      <c r="H1956" s="36"/>
     </row>
     <row r="1957" spans="6:8">
+      <c r="F1957" s="36"/>
       <c r="H1957" s="36"/>
     </row>
-    <row r="1959" spans="6:8">
-      <c r="H1959" s="36"/>
+    <row r="1958" spans="6:8">
+      <c r="H1958" s="36"/>
     </row>
     <row r="1960" spans="6:8">
-      <c r="F1960" s="36"/>
       <c r="H1960" s="36"/>
     </row>
-    <row r="1961" spans="6:8">
-      <c r="H1961" s="36"/>
-    </row>
-    <row r="1963" spans="6:8">
-      <c r="H1963" s="36"/>
+    <row r="1962" spans="6:8">
+      <c r="H1962" s="36"/>
+    </row>
+    <row r="1964" spans="6:8">
+      <c r="H1964" s="36"/>
     </row>
     <row r="1965" spans="6:8">
+      <c r="F1965" s="36"/>
       <c r="H1965" s="36"/>
     </row>
-    <row r="1967" spans="6:8">
-      <c r="H1967" s="36"/>
-    </row>
-    <row r="1969" spans="6:8">
-      <c r="F1969" s="36"/>
-      <c r="H1969" s="36"/>
-    </row>
-    <row r="1977" spans="6:8">
-      <c r="F1977" s="36"/>
-    </row>
-    <row r="1985" spans="6:8">
-      <c r="F1985" s="36"/>
-    </row>
-    <row r="1992" spans="6:8">
-      <c r="F1992" s="36"/>
-      <c r="H1992" s="36"/>
-    </row>
-    <row r="2008" spans="6:8">
-      <c r="F2008" s="37"/>
-      <c r="H2008" s="37"/>
-    </row>
-    <row r="2009" spans="6:8">
-      <c r="F2009" s="37"/>
-    </row>
-    <row r="2012" spans="6:8">
-      <c r="F2012" s="37"/>
-      <c r="H2012" s="37"/>
+    <row r="1966" spans="6:8">
+      <c r="H1966" s="36"/>
+    </row>
+    <row r="1968" spans="6:8">
+      <c r="H1968" s="36"/>
+    </row>
+    <row r="1970" spans="6:8">
+      <c r="H1970" s="36"/>
+    </row>
+    <row r="1972" spans="6:8">
+      <c r="H1972" s="36"/>
+    </row>
+    <row r="1974" spans="6:8">
+      <c r="F1974" s="36"/>
+      <c r="H1974" s="36"/>
+    </row>
+    <row r="1982" spans="6:8">
+      <c r="F1982" s="36"/>
+    </row>
+    <row r="1990" spans="6:8">
+      <c r="F1990" s="36"/>
+    </row>
+    <row r="1997" spans="6:8">
+      <c r="F1997" s="36"/>
+      <c r="H1997" s="36"/>
     </row>
     <row r="2013" spans="6:8">
-      <c r="F2013" s="36"/>
-    </row>
-    <row r="2026" spans="6:8">
-      <c r="F2026" s="36"/>
-      <c r="H2026" s="36"/>
-    </row>
-    <row r="2041" spans="6:8">
-      <c r="F2041" s="37"/>
-      <c r="H2041" s="37"/>
-    </row>
-    <row r="2042" spans="6:8">
-      <c r="F2042" s="37"/>
-    </row>
-    <row r="2045" spans="6:8">
-      <c r="F2045" s="37"/>
-      <c r="H2045" s="37"/>
+      <c r="F2013" s="37"/>
+      <c r="H2013" s="37"/>
+    </row>
+    <row r="2014" spans="6:8">
+      <c r="F2014" s="37"/>
+    </row>
+    <row r="2017" spans="6:8">
+      <c r="F2017" s="37"/>
+      <c r="H2017" s="37"/>
+    </row>
+    <row r="2018" spans="6:8">
+      <c r="F2018" s="36"/>
+    </row>
+    <row r="2031" spans="6:8">
+      <c r="F2031" s="36"/>
+      <c r="H2031" s="36"/>
     </row>
     <row r="2046" spans="6:8">
-      <c r="F2046" s="36"/>
-    </row>
-    <row r="2059" spans="6:8">
-      <c r="F2059" s="36"/>
-      <c r="H2059" s="36"/>
-    </row>
-    <row r="2074" spans="6:8">
-      <c r="F2074" s="37"/>
-      <c r="H2074" s="37"/>
-    </row>
-    <row r="2075" spans="6:8">
-      <c r="F2075" s="37"/>
-    </row>
-    <row r="2078" spans="6:8">
-      <c r="F2078" s="37"/>
-      <c r="H2078" s="37"/>
+      <c r="F2046" s="37"/>
+      <c r="H2046" s="37"/>
+    </row>
+    <row r="2047" spans="6:8">
+      <c r="F2047" s="37"/>
+    </row>
+    <row r="2050" spans="6:8">
+      <c r="F2050" s="37"/>
+      <c r="H2050" s="37"/>
+    </row>
+    <row r="2051" spans="6:8">
+      <c r="F2051" s="36"/>
+    </row>
+    <row r="2064" spans="6:8">
+      <c r="F2064" s="36"/>
+      <c r="H2064" s="36"/>
     </row>
     <row r="2079" spans="6:8">
-      <c r="F2079" s="36"/>
-    </row>
-    <row r="2092" spans="6:8">
-      <c r="F2092" s="36"/>
-      <c r="H2092" s="36"/>
-    </row>
-    <row r="2100" spans="6:8">
-      <c r="F2100" s="36"/>
-      <c r="G2100" s="36"/>
-      <c r="H2100" s="36"/>
-    </row>
-    <row r="2107" spans="6:8">
-      <c r="F2107" s="37"/>
-      <c r="H2107" s="37"/>
-    </row>
-    <row r="2108" spans="6:8">
-      <c r="F2108" s="37"/>
-    </row>
-    <row r="2111" spans="6:8">
-      <c r="F2111" s="37"/>
-      <c r="H2111" s="37"/>
+      <c r="F2079" s="37"/>
+      <c r="H2079" s="37"/>
+    </row>
+    <row r="2080" spans="6:8">
+      <c r="F2080" s="37"/>
+    </row>
+    <row r="2083" spans="6:8">
+      <c r="F2083" s="37"/>
+      <c r="H2083" s="37"/>
+    </row>
+    <row r="2084" spans="6:8">
+      <c r="F2084" s="36"/>
+    </row>
+    <row r="2097" spans="6:8">
+      <c r="F2097" s="36"/>
+      <c r="H2097" s="36"/>
+    </row>
+    <row r="2105" spans="6:8">
+      <c r="F2105" s="36"/>
+      <c r="G2105" s="36"/>
+      <c r="H2105" s="36"/>
     </row>
     <row r="2112" spans="6:8">
-      <c r="F2112" s="36"/>
-    </row>
-    <row r="2125" spans="6:8">
-      <c r="F2125" s="36"/>
-      <c r="H2125" s="36"/>
-    </row>
-    <row r="2133" spans="6:8">
-      <c r="F2133" s="36"/>
-      <c r="G2133" s="36"/>
-      <c r="H2133" s="36"/>
-    </row>
-    <row r="2140" spans="6:8">
-      <c r="F2140" s="37"/>
-      <c r="H2140" s="37"/>
-    </row>
-    <row r="2141" spans="6:8">
-      <c r="F2141" s="37"/>
-    </row>
-    <row r="2144" spans="6:8">
-      <c r="F2144" s="37"/>
-      <c r="H2144" s="37"/>
+      <c r="F2112" s="37"/>
+      <c r="H2112" s="37"/>
+    </row>
+    <row r="2113" spans="6:8">
+      <c r="F2113" s="37"/>
+    </row>
+    <row r="2116" spans="6:8">
+      <c r="F2116" s="37"/>
+      <c r="H2116" s="37"/>
+    </row>
+    <row r="2117" spans="6:8">
+      <c r="F2117" s="36"/>
+    </row>
+    <row r="2130" spans="6:8">
+      <c r="F2130" s="36"/>
+      <c r="H2130" s="36"/>
+    </row>
+    <row r="2138" spans="6:8">
+      <c r="F2138" s="36"/>
+      <c r="G2138" s="36"/>
+      <c r="H2138" s="36"/>
     </row>
     <row r="2145" spans="6:8">
-      <c r="F2145" s="36"/>
-    </row>
-    <row r="2158" spans="6:8">
-      <c r="F2158" s="36"/>
-      <c r="H2158" s="36"/>
-    </row>
-    <row r="2166" spans="6:8">
-      <c r="F2166" s="36"/>
-      <c r="G2166" s="36"/>
-      <c r="H2166" s="36"/>
-    </row>
-    <row r="2173" spans="6:8">
-      <c r="F2173" s="37"/>
-      <c r="H2173" s="37"/>
-    </row>
-    <row r="2174" spans="6:8">
-      <c r="F2174" s="37"/>
-    </row>
-    <row r="2177" spans="6:8">
-      <c r="F2177" s="37"/>
-      <c r="H2177" s="37"/>
+      <c r="F2145" s="37"/>
+      <c r="H2145" s="37"/>
+    </row>
+    <row r="2146" spans="6:8">
+      <c r="F2146" s="37"/>
+    </row>
+    <row r="2149" spans="6:8">
+      <c r="F2149" s="37"/>
+      <c r="H2149" s="37"/>
+    </row>
+    <row r="2150" spans="6:8">
+      <c r="F2150" s="36"/>
+    </row>
+    <row r="2163" spans="6:8">
+      <c r="F2163" s="36"/>
+      <c r="H2163" s="36"/>
+    </row>
+    <row r="2171" spans="6:8">
+      <c r="F2171" s="36"/>
+      <c r="G2171" s="36"/>
+      <c r="H2171" s="36"/>
     </row>
     <row r="2178" spans="6:8">
-      <c r="F2178" s="36"/>
-    </row>
-    <row r="2191" spans="6:8">
-      <c r="F2191" s="36"/>
-      <c r="H2191" s="36"/>
-    </row>
-    <row r="2206" spans="6:8">
-      <c r="F2206" s="37"/>
-      <c r="H2206" s="37"/>
-    </row>
-    <row r="2207" spans="6:8">
-      <c r="F2207" s="37"/>
-    </row>
-    <row r="2210" spans="6:8">
-      <c r="F2210" s="37"/>
-      <c r="H2210" s="37"/>
+      <c r="F2178" s="37"/>
+      <c r="H2178" s="37"/>
+    </row>
+    <row r="2179" spans="6:8">
+      <c r="F2179" s="37"/>
+    </row>
+    <row r="2182" spans="6:8">
+      <c r="F2182" s="37"/>
+      <c r="H2182" s="37"/>
+    </row>
+    <row r="2183" spans="6:8">
+      <c r="F2183" s="36"/>
+    </row>
+    <row r="2196" spans="6:8">
+      <c r="F2196" s="36"/>
+      <c r="H2196" s="36"/>
     </row>
     <row r="2211" spans="6:8">
-      <c r="F2211" s="36"/>
-    </row>
-    <row r="2224" spans="6:8">
-      <c r="F2224" s="36"/>
-      <c r="H2224" s="36"/>
-    </row>
-    <row r="2239" spans="6:8">
-      <c r="F2239" s="37"/>
-      <c r="H2239" s="37"/>
-    </row>
-    <row r="2240" spans="6:8">
-      <c r="F2240" s="37"/>
-    </row>
-    <row r="2243" spans="6:8">
-      <c r="F2243" s="37"/>
-      <c r="H2243" s="37"/>
+      <c r="F2211" s="37"/>
+      <c r="H2211" s="37"/>
+    </row>
+    <row r="2212" spans="6:8">
+      <c r="F2212" s="37"/>
+    </row>
+    <row r="2215" spans="6:8">
+      <c r="F2215" s="37"/>
+      <c r="H2215" s="37"/>
+    </row>
+    <row r="2216" spans="6:8">
+      <c r="F2216" s="36"/>
+    </row>
+    <row r="2229" spans="6:8">
+      <c r="F2229" s="36"/>
+      <c r="H2229" s="36"/>
     </row>
     <row r="2244" spans="6:8">
-      <c r="F2244" s="36"/>
-    </row>
-    <row r="2257" spans="6:8">
-      <c r="F2257" s="36"/>
-      <c r="H2257" s="36"/>
-    </row>
-    <row r="2265" spans="6:8">
-      <c r="F2265" s="36"/>
-      <c r="G2265" s="36"/>
-      <c r="H2265" s="36"/>
-    </row>
-    <row r="2272" spans="6:8">
-      <c r="F2272" s="37"/>
-      <c r="H2272" s="37"/>
-    </row>
-    <row r="2273" spans="6:8">
-      <c r="F2273" s="37"/>
-    </row>
-    <row r="2276" spans="6:8">
-      <c r="F2276" s="37"/>
-      <c r="H2276" s="37"/>
+      <c r="F2244" s="37"/>
+      <c r="H2244" s="37"/>
+    </row>
+    <row r="2245" spans="6:8">
+      <c r="F2245" s="37"/>
+    </row>
+    <row r="2248" spans="6:8">
+      <c r="F2248" s="37"/>
+      <c r="H2248" s="37"/>
+    </row>
+    <row r="2249" spans="6:8">
+      <c r="F2249" s="36"/>
+    </row>
+    <row r="2262" spans="6:8">
+      <c r="F2262" s="36"/>
+      <c r="H2262" s="36"/>
+    </row>
+    <row r="2270" spans="6:8">
+      <c r="F2270" s="36"/>
+      <c r="G2270" s="36"/>
+      <c r="H2270" s="36"/>
     </row>
     <row r="2277" spans="6:8">
-      <c r="F2277" s="36"/>
-    </row>
-    <row r="2290" spans="6:8">
-      <c r="F2290" s="36"/>
-      <c r="H2290" s="36"/>
-    </row>
-    <row r="2298" spans="6:8">
-      <c r="F2298" s="36"/>
-      <c r="G2298" s="36"/>
-      <c r="H2298" s="36"/>
-    </row>
-    <row r="2305" spans="6:8">
-      <c r="F2305" s="37"/>
-      <c r="H2305" s="37"/>
-    </row>
-    <row r="2306" spans="6:8">
-      <c r="F2306" s="37"/>
-    </row>
-    <row r="2309" spans="6:8">
-      <c r="F2309" s="37"/>
-      <c r="H2309" s="37"/>
+      <c r="F2277" s="37"/>
+      <c r="H2277" s="37"/>
+    </row>
+    <row r="2278" spans="6:8">
+      <c r="F2278" s="37"/>
+    </row>
+    <row r="2281" spans="6:8">
+      <c r="F2281" s="37"/>
+      <c r="H2281" s="37"/>
+    </row>
+    <row r="2282" spans="6:8">
+      <c r="F2282" s="36"/>
+    </row>
+    <row r="2295" spans="6:8">
+      <c r="F2295" s="36"/>
+      <c r="H2295" s="36"/>
+    </row>
+    <row r="2303" spans="6:8">
+      <c r="F2303" s="36"/>
+      <c r="G2303" s="36"/>
+      <c r="H2303" s="36"/>
     </row>
     <row r="2310" spans="6:8">
-      <c r="F2310" s="36"/>
-    </row>
-    <row r="2323" spans="6:8">
-      <c r="F2323" s="36"/>
-      <c r="H2323" s="36"/>
-    </row>
-    <row r="2331" spans="6:8">
-      <c r="F2331" s="36"/>
-      <c r="G2331" s="36"/>
-      <c r="H2331" s="36"/>
-    </row>
-    <row r="2333" spans="6:8">
-      <c r="F2333" s="36"/>
-      <c r="G2333" s="36"/>
-      <c r="H2333" s="36"/>
-    </row>
-    <row r="2334" spans="6:8">
-      <c r="F2334" s="36"/>
-      <c r="G2334" s="36"/>
-      <c r="H2334" s="36"/>
-    </row>
-    <row r="2335" spans="6:8">
-      <c r="F2335" s="36"/>
-      <c r="G2335" s="36"/>
-      <c r="H2335" s="36"/>
+      <c r="F2310" s="37"/>
+      <c r="H2310" s="37"/>
+    </row>
+    <row r="2311" spans="6:8">
+      <c r="F2311" s="37"/>
+    </row>
+    <row r="2314" spans="6:8">
+      <c r="F2314" s="37"/>
+      <c r="H2314" s="37"/>
+    </row>
+    <row r="2315" spans="6:8">
+      <c r="F2315" s="36"/>
+    </row>
+    <row r="2328" spans="6:8">
+      <c r="F2328" s="36"/>
+      <c r="H2328" s="36"/>
     </row>
     <row r="2336" spans="6:8">
       <c r="F2336" s="36"/>
       <c r="G2336" s="36"/>
       <c r="H2336" s="36"/>
     </row>
-    <row r="2337" spans="6:8">
-      <c r="F2337" s="36"/>
-      <c r="G2337" s="36"/>
-      <c r="H2337" s="36"/>
-    </row>
     <row r="2338" spans="6:8">
       <c r="F2338" s="36"/>
       <c r="G2338" s="36"/>
@@ -10694,76 +10899,76 @@
       <c r="G2360" s="36"/>
       <c r="H2360" s="36"/>
     </row>
+    <row r="2361" spans="6:8">
+      <c r="F2361" s="36"/>
+      <c r="G2361" s="36"/>
+      <c r="H2361" s="36"/>
+    </row>
     <row r="2362" spans="6:8">
       <c r="F2362" s="36"/>
       <c r="G2362" s="36"/>
       <c r="H2362" s="36"/>
     </row>
-    <row r="2375" spans="6:8">
-      <c r="F2375" s="36"/>
-      <c r="G2375" s="36"/>
-      <c r="H2375" s="36"/>
-    </row>
-    <row r="2389" spans="6:8">
-      <c r="F2389" s="36"/>
-      <c r="G2389" s="36"/>
-      <c r="H2389" s="36"/>
-    </row>
-    <row r="2391" spans="6:8">
-      <c r="F2391" s="36"/>
-      <c r="G2391" s="36"/>
-      <c r="H2391" s="36"/>
-    </row>
-    <row r="2404" spans="6:8">
-      <c r="F2404" s="36"/>
-      <c r="G2404" s="36"/>
-      <c r="H2404" s="36"/>
-    </row>
-    <row r="2418" spans="6:8">
-      <c r="F2418" s="36"/>
-      <c r="G2418" s="36"/>
-      <c r="H2418" s="36"/>
-    </row>
-    <row r="2420" spans="6:8">
-      <c r="F2420" s="36"/>
-      <c r="G2420" s="36"/>
-      <c r="H2420" s="36"/>
-    </row>
-    <row r="2433" spans="6:8">
-      <c r="F2433" s="36"/>
-      <c r="G2433" s="36"/>
-      <c r="H2433" s="36"/>
-    </row>
-    <row r="2447" spans="6:8">
-      <c r="F2447" s="36"/>
-      <c r="G2447" s="36"/>
-      <c r="H2447" s="36"/>
-    </row>
-    <row r="2450" spans="6:8">
-      <c r="F2450" s="36"/>
-      <c r="G2450" s="36"/>
-      <c r="H2450" s="36"/>
-    </row>
-    <row r="2451" spans="6:8">
-      <c r="F2451" s="36"/>
-      <c r="G2451" s="36"/>
-      <c r="H2451" s="36"/>
+    <row r="2363" spans="6:8">
+      <c r="F2363" s="36"/>
+      <c r="G2363" s="36"/>
+      <c r="H2363" s="36"/>
+    </row>
+    <row r="2364" spans="6:8">
+      <c r="F2364" s="36"/>
+      <c r="G2364" s="36"/>
+      <c r="H2364" s="36"/>
+    </row>
+    <row r="2365" spans="6:8">
+      <c r="F2365" s="36"/>
+      <c r="G2365" s="36"/>
+      <c r="H2365" s="36"/>
+    </row>
+    <row r="2367" spans="6:8">
+      <c r="F2367" s="36"/>
+      <c r="G2367" s="36"/>
+      <c r="H2367" s="36"/>
+    </row>
+    <row r="2380" spans="6:8">
+      <c r="F2380" s="36"/>
+      <c r="G2380" s="36"/>
+      <c r="H2380" s="36"/>
+    </row>
+    <row r="2394" spans="6:8">
+      <c r="F2394" s="36"/>
+      <c r="G2394" s="36"/>
+      <c r="H2394" s="36"/>
+    </row>
+    <row r="2396" spans="6:8">
+      <c r="F2396" s="36"/>
+      <c r="G2396" s="36"/>
+      <c r="H2396" s="36"/>
+    </row>
+    <row r="2409" spans="6:8">
+      <c r="F2409" s="36"/>
+      <c r="G2409" s="36"/>
+      <c r="H2409" s="36"/>
+    </row>
+    <row r="2423" spans="6:8">
+      <c r="F2423" s="36"/>
+      <c r="G2423" s="36"/>
+      <c r="H2423" s="36"/>
+    </row>
+    <row r="2425" spans="6:8">
+      <c r="F2425" s="36"/>
+      <c r="G2425" s="36"/>
+      <c r="H2425" s="36"/>
+    </row>
+    <row r="2438" spans="6:8">
+      <c r="F2438" s="36"/>
+      <c r="G2438" s="36"/>
+      <c r="H2438" s="36"/>
     </row>
     <row r="2452" spans="6:8">
       <c r="F2452" s="36"/>
       <c r="G2452" s="36"/>
       <c r="H2452" s="36"/>
     </row>
-    <row r="2453" spans="6:8">
-      <c r="F2453" s="36"/>
-      <c r="G2453" s="36"/>
-      <c r="H2453" s="36"/>
-    </row>
-    <row r="2454" spans="6:8">
-      <c r="F2454" s="36"/>
-      <c r="G2454" s="36"/>
-      <c r="H2454" s="36"/>
-    </row>
     <row r="2455" spans="6:8">
       <c r="F2455" s="36"/>
       <c r="G2455" s="36"/>
@@ -10809,110 +11014,135 @@
       <c r="G2463" s="36"/>
       <c r="H2463" s="36"/>
     </row>
-    <row r="2472" spans="6:8">
-      <c r="F2472" s="36"/>
-      <c r="G2472" s="36"/>
-      <c r="H2472" s="36"/>
-    </row>
-    <row r="2489" spans="6:8">
-      <c r="F2489" s="36"/>
-      <c r="G2489" s="36"/>
-      <c r="H2489" s="36"/>
-    </row>
-    <row r="2506" spans="6:8">
-      <c r="F2506" s="36"/>
-      <c r="G2506" s="36"/>
-      <c r="H2506" s="36"/>
-    </row>
-    <row r="2523" spans="6:8">
-      <c r="F2523" s="36"/>
-      <c r="G2523" s="36"/>
-      <c r="H2523" s="36"/>
-    </row>
-    <row r="2540" spans="6:6">
-      <c r="F2540" s="36"/>
-    </row>
-    <row r="2557" spans="6:6">
-      <c r="F2557" s="36"/>
-    </row>
-    <row r="2574" spans="6:6">
-      <c r="F2574" s="36"/>
-    </row>
-    <row r="2591" spans="6:6">
-      <c r="F2591" s="36"/>
-    </row>
-    <row r="2608" spans="6:6">
-      <c r="F2608" s="36"/>
-    </row>
-    <row r="2625" spans="6:6">
-      <c r="F2625" s="36"/>
-    </row>
-    <row r="2642" spans="6:6">
-      <c r="F2642" s="36"/>
-    </row>
-    <row r="2659" spans="6:8">
-      <c r="F2659" s="36"/>
-      <c r="H2659" s="36"/>
-    </row>
-    <row r="2676" spans="6:6">
-      <c r="F2676" s="36"/>
-    </row>
-    <row r="2710" spans="6:6">
-      <c r="F2710" s="36"/>
-    </row>
-    <row r="2727" spans="6:6">
-      <c r="F2727" s="36"/>
-    </row>
-    <row r="2750" spans="6:8">
-      <c r="F2750" s="36"/>
-      <c r="H2750" s="36"/>
-    </row>
-    <row r="2771" spans="6:6">
-      <c r="F2771" s="36"/>
-    </row>
-    <row r="2786" spans="6:8">
-      <c r="F2786" s="36"/>
-      <c r="G2786" s="36"/>
-      <c r="H2786" s="36"/>
-    </row>
-    <row r="2801" spans="6:8">
-      <c r="F2801" s="36"/>
-      <c r="H2801" s="36"/>
-    </row>
-    <row r="2816" spans="6:8">
-      <c r="F2816" s="36"/>
-      <c r="G2816" s="36"/>
-      <c r="H2816" s="36"/>
-    </row>
-    <row r="2832" spans="6:8">
-      <c r="F2832" s="36"/>
-      <c r="G2832" s="36"/>
-      <c r="H2832" s="36"/>
-    </row>
-    <row r="2840" spans="6:8">
-      <c r="F2840" s="36"/>
-      <c r="G2840" s="36"/>
-      <c r="H2840" s="36"/>
-    </row>
-    <row r="2868" spans="6:8">
-      <c r="F2868" s="36"/>
-      <c r="G2868" s="36"/>
-      <c r="H2868" s="36"/>
-    </row>
-    <row r="2876" spans="6:8">
-      <c r="F2876" s="36"/>
-      <c r="G2876" s="36"/>
-      <c r="H2876" s="36"/>
-    </row>
-    <row r="2883" spans="6:8">
-      <c r="F2883" s="36"/>
-      <c r="G2883" s="36"/>
-      <c r="H2883" s="36"/>
+    <row r="2464" spans="6:8">
+      <c r="F2464" s="36"/>
+      <c r="G2464" s="36"/>
+      <c r="H2464" s="36"/>
+    </row>
+    <row r="2465" spans="6:8">
+      <c r="F2465" s="36"/>
+      <c r="G2465" s="36"/>
+      <c r="H2465" s="36"/>
+    </row>
+    <row r="2466" spans="6:8">
+      <c r="F2466" s="36"/>
+      <c r="G2466" s="36"/>
+      <c r="H2466" s="36"/>
+    </row>
+    <row r="2467" spans="6:8">
+      <c r="F2467" s="36"/>
+      <c r="G2467" s="36"/>
+      <c r="H2467" s="36"/>
+    </row>
+    <row r="2468" spans="6:8">
+      <c r="F2468" s="36"/>
+      <c r="G2468" s="36"/>
+      <c r="H2468" s="36"/>
+    </row>
+    <row r="2477" spans="6:8">
+      <c r="F2477" s="36"/>
+      <c r="G2477" s="36"/>
+      <c r="H2477" s="36"/>
+    </row>
+    <row r="2494" spans="6:8">
+      <c r="F2494" s="36"/>
+      <c r="G2494" s="36"/>
+      <c r="H2494" s="36"/>
+    </row>
+    <row r="2511" spans="6:8">
+      <c r="F2511" s="36"/>
+      <c r="G2511" s="36"/>
+      <c r="H2511" s="36"/>
+    </row>
+    <row r="2528" spans="6:8">
+      <c r="F2528" s="36"/>
+      <c r="G2528" s="36"/>
+      <c r="H2528" s="36"/>
+    </row>
+    <row r="2545" spans="6:6">
+      <c r="F2545" s="36"/>
+    </row>
+    <row r="2562" spans="6:6">
+      <c r="F2562" s="36"/>
+    </row>
+    <row r="2579" spans="6:6">
+      <c r="F2579" s="36"/>
+    </row>
+    <row r="2596" spans="6:6">
+      <c r="F2596" s="36"/>
+    </row>
+    <row r="2613" spans="6:6">
+      <c r="F2613" s="36"/>
+    </row>
+    <row r="2630" spans="6:6">
+      <c r="F2630" s="36"/>
+    </row>
+    <row r="2647" spans="6:6">
+      <c r="F2647" s="36"/>
+    </row>
+    <row r="2664" spans="6:8">
+      <c r="F2664" s="36"/>
+      <c r="H2664" s="36"/>
+    </row>
+    <row r="2681" spans="6:6">
+      <c r="F2681" s="36"/>
+    </row>
+    <row r="2715" spans="6:6">
+      <c r="F2715" s="36"/>
+    </row>
+    <row r="2732" spans="6:6">
+      <c r="F2732" s="36"/>
+    </row>
+    <row r="2755" spans="6:8">
+      <c r="F2755" s="36"/>
+      <c r="H2755" s="36"/>
+    </row>
+    <row r="2776" spans="6:6">
+      <c r="F2776" s="36"/>
+    </row>
+    <row r="2791" spans="6:8">
+      <c r="F2791" s="36"/>
+      <c r="G2791" s="36"/>
+      <c r="H2791" s="36"/>
+    </row>
+    <row r="2806" spans="6:8">
+      <c r="F2806" s="36"/>
+      <c r="H2806" s="36"/>
+    </row>
+    <row r="2821" spans="6:8">
+      <c r="F2821" s="36"/>
+      <c r="G2821" s="36"/>
+      <c r="H2821" s="36"/>
+    </row>
+    <row r="2837" spans="6:8">
+      <c r="F2837" s="36"/>
+      <c r="G2837" s="36"/>
+      <c r="H2837" s="36"/>
+    </row>
+    <row r="2845" spans="6:8">
+      <c r="F2845" s="36"/>
+      <c r="G2845" s="36"/>
+      <c r="H2845" s="36"/>
+    </row>
+    <row r="2873" spans="6:8">
+      <c r="F2873" s="36"/>
+      <c r="G2873" s="36"/>
+      <c r="H2873" s="36"/>
+    </row>
+    <row r="2881" spans="6:8">
+      <c r="F2881" s="36"/>
+      <c r="G2881" s="36"/>
+      <c r="H2881" s="36"/>
+    </row>
+    <row r="2888" spans="6:8">
+      <c r="F2888" s="36"/>
+      <c r="G2888" s="36"/>
+      <c r="H2888" s="36"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:J131">
-    <sortCondition ref="A9:A131"/>
-    <sortCondition ref="C9:C131"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:J136">
+    <sortCondition ref="A9:A136"/>
+    <sortCondition ref="C9:C136"/>
   </sortState>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10987,7 +11217,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -11001,7 +11231,7 @@
         <v>51</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -11015,7 +11245,7 @@
         <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -11029,7 +11259,7 @@
         <v>139</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -11043,7 +11273,7 @@
         <v>140</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -11057,7 +11287,7 @@
         <v>141</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -11071,7 +11301,7 @@
         <v>142</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -11085,7 +11315,7 @@
         <v>84</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -11099,7 +11329,7 @@
         <v>94</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -11113,7 +11343,7 @@
         <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -11127,7 +11357,7 @@
         <v>94</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -11141,7 +11371,7 @@
         <v>94</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -11155,7 +11385,7 @@
         <v>94</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -11169,7 +11399,7 @@
         <v>94</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -11183,7 +11413,7 @@
         <v>94</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -11197,7 +11427,7 @@
         <v>94</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -11208,10 +11438,10 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -11222,10 +11452,10 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -11239,7 +11469,7 @@
         <v>102</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -11253,7 +11483,7 @@
         <v>118</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -11267,7 +11497,7 @@
         <v>118</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -11281,7 +11511,7 @@
         <v>118</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -11295,7 +11525,7 @@
         <v>118</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -11309,7 +11539,7 @@
         <v>123</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -11323,7 +11553,7 @@
         <v>127</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -11337,7 +11567,7 @@
         <v>132</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -11351,7 +11581,7 @@
         <v>138</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -11365,7 +11595,7 @@
         <v>148</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -11433,7 +11663,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -11447,7 +11677,7 @@
         <v>58</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -11461,7 +11691,7 @@
         <v>68</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -11475,7 +11705,7 @@
         <v>190</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -11489,7 +11719,7 @@
         <v>191</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -11503,7 +11733,7 @@
         <v>194</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -11517,7 +11747,7 @@
         <v>77</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -11531,7 +11761,7 @@
         <v>110</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -11545,7 +11775,7 @@
         <v>113</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -11559,7 +11789,7 @@
         <v>81</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -11573,7 +11803,7 @@
         <v>110</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -11587,7 +11817,7 @@
         <v>163</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -11601,7 +11831,7 @@
         <v>159</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -11615,7 +11845,7 @@
         <v>161</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
@@ -11629,7 +11859,7 @@
         <v>101</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -11643,7 +11873,7 @@
         <v>110</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -11657,7 +11887,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -11671,7 +11901,7 @@
         <v>110</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -11685,7 +11915,7 @@
         <v>163</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -11699,7 +11929,7 @@
         <v>163</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -11713,7 +11943,7 @@
         <v>163</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -11727,7 +11957,7 @@
         <v>163</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -11741,7 +11971,7 @@
         <v>163</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -11755,7 +11985,7 @@
         <v>163</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -11769,7 +11999,7 @@
         <v>163</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -11783,7 +12013,7 @@
         <v>163</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -11797,7 +12027,7 @@
         <v>196</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -11811,7 +12041,7 @@
         <v>196</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -11825,7 +12055,7 @@
         <v>196</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -11839,7 +12069,7 @@
         <v>196</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -11853,7 +12083,7 @@
         <v>196</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -11867,7 +12097,7 @@
         <v>196</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -11881,7 +12111,7 @@
         <v>196</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -11895,7 +12125,7 @@
         <v>196</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -12001,7 +12231,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -12015,7 +12245,7 @@
         <v>47</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -12111,7 +12341,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -12125,7 +12355,7 @@
         <v>49</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -12139,7 +12369,7 @@
         <v>59</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -12153,7 +12383,7 @@
         <v>186</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -12209,7 +12439,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B4" s="4"/>
     </row>
@@ -12221,16 +12451,16 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B7" s="5"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -12311,63 +12541,63 @@
         <v>35</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C9" t="s">
         <v>57</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" t="s">
         <v>223</v>
       </c>
-      <c r="C12" t="s">
-        <v>225</v>
-      </c>
-      <c r="D12" t="s">
-        <v>224</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" spans="1:5">
